--- a/experiments/analysis/tables/main_comparison_tables_2026-09-30.xlsx
+++ b/experiments/analysis/tables/main_comparison_tables_2026-09-30.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="127">
   <si>
     <r>
       <rPr>
@@ -1143,6 +1143,229 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11h </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主块按用户选定口径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">剔除评估种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">128</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两臂同剔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原因是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8STD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">amb_0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在这两个种子被 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Aungier St </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">右转排队回溢卡在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">389281 (45 s / 90 s), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">属路线撞上非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">让行口的外部瓶颈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子的结果作为参考块保留在同一工作表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">总览里两行都有。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -1513,7 +1736,145 @@
     <t xml:space="preserve">Dublin 02h: Dublin 02:00, ambulance probe route, best checkpoints (8STD: exp287 ep770, GS-EN</t>
   </si>
   <si>
-    <t xml:space="preserve">Dublin 11h: Dublin 11:00, ambulance probe route, best checkpoints (8STD: exp208 ep240, GS-EN</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11h: Dublin 11:00, best </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检查点 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">剔除种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">128</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132 (8STD: exp208 ep240, GS-ENUM: exp211</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11h: Dublin 11:00, best </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检查点 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8STD: exp208 ep240, GS-ENUM: exp211 ep215)  </t>
+    </r>
   </si>
   <si>
     <r>
@@ -1629,7 +1990,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">123-132); </t>
+      <t xml:space="preserve">123, 124, 125, 126, 127, 128, 129, 130, 131, 132); </t>
     </r>
     <r>
       <rPr>
@@ -3255,7 +3616,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">123-132); </t>
+      <t xml:space="preserve">123, 124, 125, 126, 127, 128, 129, 130, 131, 132); </t>
     </r>
     <r>
       <rPr>
@@ -3571,7 +3932,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">123-132); </t>
+      <t xml:space="preserve">123, 124, 125, 126, 127, 128, 129, 130, 131, 132); </t>
     </r>
     <r>
       <rPr>
@@ -4910,6 +5271,635 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">× 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">评估种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">123, 124, 125, 126, 127, 129, 130, 131); </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口径 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用户选定</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">剔除种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">128</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两臂同剔</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">; 8STD </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">amb_0 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在这两个种子被 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Aungier St </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回溢卡在 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">389281)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数据源</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: experiments/analysis/figures/main_comparison_11h_best10seeds_SELECTED_excl128_132_2026-09-30_en.json (</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与同名 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">png </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同源</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">); </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">异常种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">对称规则</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">; Tukey </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">离群种子</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11:00, best </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检查点 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">剔除种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">128</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132 (8STD: exp208 ep240, GS-ENUM: exp211 ep215)  [</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用户选定口径</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">8/8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11h: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同路线同时刻换车型 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">救护车 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公交探针</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), best </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检查点</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11h (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种子</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): best </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检查点 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">× 10 </t>
     </r>
     <r>
@@ -4948,7 +5938,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">123-132); </t>
+      <t xml:space="preserve">123, 124, 125, 126, 127, 128, 129, 130, 131, 132); </t>
     </r>
     <r>
       <rPr>
@@ -4967,7 +5957,172 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A (best </t>
+      <t xml:space="preserve">A, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未剔除</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数据源</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: experiments/analysis/figures/main_comparison_11h_best10seeds_2026-09-30_en.json (</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与同名 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">png </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同源</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">); </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">异常种子 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">对称规则</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">; Tukey </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">离群种子</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dublin 11:00, best </t>
     </r>
     <r>
       <rPr>
@@ -5005,317 +6160,45 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) + </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">口径 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">尾 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次评估</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">两块</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">数据源</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: experiments/analysis/figures/main_comparison_11h_best10seeds_2026-09-30_en.json (</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与同名 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">png </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同源</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">); </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">异常种子 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">对称规则</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">): </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">无</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">; Tukey </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">离群种子</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">无</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 11:00, ambulance probe route, best checkpoints (8STD: exp208 ep240, GS-ENUM: exp211 ep215), 10 evaluation seeds</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Dublin 11h: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同路线同时刻换车型 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">救护车 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公交探针</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), best </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">检查点</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 10 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">种子</t>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8STD: exp208 ep240, GS-ENUM: exp211 ep215)  [</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
     </r>
   </si>
   <si>
@@ -5938,7 +6821,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="160"/>
@@ -5993,8 +6876,13 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6013,7 +6901,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="80"/>
@@ -6023,50 +6911,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">1x1!B9</f>
@@ -6107,10 +6995,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">1x1!B24</f>
@@ -6151,10 +7039,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">1x3!B9</f>
@@ -6195,10 +7083,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">'Dublin 02h'!B9</f>
@@ -6239,42 +7127,42 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">'Dublin 11h'!B9</f>
-        <v>2.65781293270989</v>
+        <v>2.67921871733148</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">'Dublin 11h'!D9</f>
-        <v>1.92889250624194</v>
+        <v>1.95467515661745</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">IF(C7=0,"",D7/C7-1)</f>
-        <v>-0.274255730152066</v>
+        <v>-0.270430911827787</v>
       </c>
       <c r="F7" s="10" t="n">
         <f aca="false">'Dublin 11h'!B10</f>
-        <v>2.76959314951954</v>
+        <v>2.79027457863489</v>
       </c>
       <c r="G7" s="10" t="n">
         <f aca="false">'Dublin 11h'!D10</f>
-        <v>2.02964186697718</v>
+        <v>2.05471571023817</v>
       </c>
       <c r="H7" s="12" t="n">
         <f aca="false">IF(F7=0,"",G7/F7-1)</f>
-        <v>-0.267169668104763</v>
+        <v>-0.263615227701564</v>
       </c>
       <c r="I7" s="9" t="str">
         <f aca="false">'Dublin 11h'!G10</f>
-        <v>10/10</v>
+        <v>8/8</v>
       </c>
       <c r="J7" s="9" t="str">
         <f aca="false">'Dublin 11h'!B11</f>
-        <v>pass (tol. 5 s)</v>
+        <v>pass</v>
       </c>
       <c r="K7" s="9" t="str">
         <f aca="false">'Dublin 11h'!D11</f>
@@ -6283,45 +7171,89 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">'Dublin 11h'!B39</f>
-        <v>4.75</v>
+        <f aca="false">'Dublin 11h'!B42</f>
+        <v>2.65781293270989</v>
       </c>
       <c r="D8" s="10" t="n">
-        <f aca="false">'Dublin 11h'!D39</f>
-        <v>2.38</v>
+        <f aca="false">'Dublin 11h'!D42</f>
+        <v>1.92889250624194</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">IF(C8=0,"",D8/C8-1)</f>
-        <v>-0.498947368421053</v>
+        <v>-0.274255730152066</v>
       </c>
       <c r="F8" s="10" t="n">
-        <f aca="false">'Dublin 11h'!B40</f>
-        <v>4.89</v>
+        <f aca="false">'Dublin 11h'!B43</f>
+        <v>2.76959314951954</v>
       </c>
       <c r="G8" s="10" t="n">
-        <f aca="false">'Dublin 11h'!D40</f>
-        <v>2.48</v>
+        <f aca="false">'Dublin 11h'!D43</f>
+        <v>2.02964186697718</v>
       </c>
       <c r="H8" s="12" t="n">
         <f aca="false">IF(F8=0,"",G8/F8-1)</f>
+        <v>-0.267169668104763</v>
+      </c>
+      <c r="I8" s="9" t="str">
+        <f aca="false">'Dublin 11h'!G43</f>
+        <v>10/10</v>
+      </c>
+      <c r="J8" s="9" t="str">
+        <f aca="false">'Dublin 11h'!B44</f>
+        <v>pass (tol. 5 s)</v>
+      </c>
+      <c r="K8" s="9" t="str">
+        <f aca="false">'Dublin 11h'!D44</f>
+        <v>pass</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <f aca="false">'Dublin 11h'!B57</f>
+        <v>4.75</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <f aca="false">'Dublin 11h'!D57</f>
+        <v>2.38</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <f aca="false">IF(C9=0,"",D9/C9-1)</f>
+        <v>-0.498947368421053</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <f aca="false">'Dublin 11h'!B58</f>
+        <v>4.89</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <f aca="false">'Dublin 11h'!D58</f>
+        <v>2.48</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <f aca="false">IF(F9=0,"",G9/F9-1)</f>
         <v>-0.492842535787321</v>
       </c>
-      <c r="I8" s="9" t="str">
-        <f aca="false">'Dublin 11h'!G40</f>
+      <c r="I9" s="9" t="str">
+        <f aca="false">'Dublin 11h'!G58</f>
         <v>40/40</v>
       </c>
-      <c r="J8" s="9" t="str">
-        <f aca="false">'Dublin 11h'!B41</f>
+      <c r="J9" s="9" t="str">
+        <f aca="false">'Dublin 11h'!B59</f>
         <v>pass</v>
       </c>
-      <c r="K8" s="9" t="str">
-        <f aca="false">'Dublin 11h'!D41</f>
+      <c r="K9" s="9" t="str">
+        <f aca="false">'Dublin 11h'!D59</f>
         <v>pass</v>
       </c>
     </row>
@@ -6351,17 +7283,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -6373,33 +7305,33 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>32.2318059299191</v>
@@ -6422,7 +7354,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>6.7625</v>
@@ -6445,7 +7377,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>4.25</v>
@@ -6465,12 +7397,12 @@
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>30.8662898334041</v>
@@ -6493,7 +7425,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>31.809305222372</v>
@@ -6512,13 +7444,13 @@
         <v>0.0816927561102245</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -6533,12 +7465,12 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>1.12789757412399</v>
@@ -6561,7 +7493,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>0.8325</v>
@@ -6584,7 +7516,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>0.533333333333333</v>
@@ -6604,12 +7536,12 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>1.11162989392257</v>
@@ -6632,7 +7564,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>1.17537199236298</v>
@@ -6651,13 +7583,13 @@
         <v>0.0793823066215862</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" s="9" t="str">
         <f aca="false">IF(AND(B14&lt;=B13,B13&lt;=B12),"pass",IF(AND(B14-B13&lt;=0.5,B13-B12&lt;=0.5),"pass (tol.)","fail"))</f>
@@ -6675,7 +7607,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -6687,33 +7619,33 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="17" t="n">
         <v>31.7303084755915</v>
@@ -6736,7 +7668,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" s="17" t="n">
         <v>6.75</v>
@@ -6759,7 +7691,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>3.98148148148148</v>
@@ -6779,12 +7711,12 @@
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>30.3949575643627</v>
@@ -6807,7 +7739,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" s="17" t="n">
         <v>31.3218402715384</v>
@@ -6826,13 +7758,13 @@
         <v>0.112700369720723</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B26" s="9" t="str">
         <f aca="false">IF(AND(B23&lt;=B22,B22&lt;=B21),"pass",IF(AND(B23-B22&lt;=5,B22-B21&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -6847,12 +7779,12 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B27" s="17" t="n">
         <v>1.12144354597185</v>
@@ -6875,7 +7807,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>0.830555555555555</v>
@@ -6898,7 +7830,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B29" s="17" t="n">
         <v>0.481481481481482</v>
@@ -6918,12 +7850,12 @@
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B30" s="17" t="n">
         <v>1.10534956366486</v>
@@ -6946,7 +7878,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B31" s="17" t="n">
         <v>1.16851061445543</v>
@@ -6965,13 +7897,13 @@
         <v>0.0954842192013747</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B32" s="9" t="str">
         <f aca="false">IF(AND(B29&lt;=B28,B28&lt;=B27),"pass",IF(AND(B29-B28&lt;=0.5,B28-B27&lt;=0.5),"pass (tol.)","fail"))</f>
@@ -6989,7 +7921,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -7001,48 +7933,48 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>31.7587601078167</v>
@@ -7085,7 +8017,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>1.0633423180593</v>
@@ -7128,7 +8060,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>5.5</v>
@@ -7171,7 +8103,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>0.675</v>
@@ -7214,7 +8146,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B40" s="10" t="n">
         <v>5</v>
@@ -7257,7 +8189,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B41" s="10" t="n">
         <v>0.5</v>
@@ -7300,7 +8232,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B42" s="10" t="n">
         <v>30.3507653061224</v>
@@ -7343,7 +8275,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>1.04209183673469</v>
@@ -7386,7 +8318,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>32.243935309973</v>
@@ -7429,7 +8361,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>1.17250673854447</v>
@@ -7472,7 +8404,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>6.125</v>
@@ -7515,7 +8447,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>0.65</v>
@@ -7558,7 +8490,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>7.5</v>
@@ -7601,7 +8533,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>0.5</v>
@@ -7644,7 +8576,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>30.8482142857143</v>
@@ -7687,7 +8619,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>1.14413265306123</v>
@@ -7759,17 +8691,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -7781,33 +8713,33 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>25.3515894955079</v>
@@ -7830,7 +8762,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>4.70416666666667</v>
@@ -7853,7 +8785,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>1.74603174603175</v>
@@ -7873,12 +8805,12 @@
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>23.7536031177601</v>
@@ -7901,7 +8833,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>24.792079465177</v>
@@ -7920,13 +8852,13 @@
         <v>0.165313174703693</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -7941,12 +8873,12 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>1.02161944252476</v>
@@ -7969,7 +8901,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>0.624166666666667</v>
@@ -7992,7 +8924,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>0.285714285714286</v>
@@ -8012,12 +8944,12 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>0.990637030580086</v>
@@ -8040,7 +8972,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>1.06456347039853</v>
@@ -8059,13 +8991,13 @@
         <v>0.0944559589258516</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" s="9" t="str">
         <f aca="false">IF(AND(B14&lt;=B13,B13&lt;=B12),"pass",IF(AND(B14-B13&lt;=0.5,B13-B12&lt;=0.5),"pass (tol.)","fail"))</f>
@@ -8083,7 +9015,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -8095,48 +9027,48 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>24.4874452891039</v>
@@ -8179,7 +9111,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>1.00714121170237</v>
@@ -8222,7 +9154,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>4.45833333333333</v>
@@ -8265,7 +9197,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>0.575</v>
@@ -8308,7 +9240,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>0</v>
@@ -8345,7 +9277,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>0</v>
@@ -8382,7 +9314,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>22.9243679626089</v>
@@ -8425,7 +9357,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>0.972806458466114</v>
@@ -8468,7 +9400,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>29.7800046072334</v>
@@ -8511,7 +9443,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>1.11161022805805</v>
@@ -8554,7 +9486,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>8.54166666666667</v>
@@ -8597,7 +9529,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>0.883333333333333</v>
@@ -8640,7 +9572,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>6.66666666666667</v>
@@ -8677,7 +9609,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>0.666666666666667</v>
@@ -8714,7 +9646,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>28.1261950286807</v>
@@ -8757,7 +9689,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>1.09358402379435</v>
@@ -8828,17 +9760,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -8850,33 +9782,33 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>0.764315207480353</v>
@@ -8899,7 +9831,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>0.399404761904762</v>
@@ -8922,7 +9854,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>0.375</v>
@@ -8942,12 +9874,12 @@
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>0.759914434999951</v>
@@ -8970,7 +9902,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>0.770377529184126</v>
@@ -8989,13 +9921,13 @@
         <v>-0.134956147874481</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -9010,12 +9942,12 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>0.10846497828997</v>
@@ -9038,7 +9970,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>0.0602380952380952</v>
@@ -9061,7 +9993,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.075</v>
@@ -9081,12 +10013,12 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>0.107910373615727</v>
@@ -9109,7 +10041,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>0.109572337766947</v>
@@ -9128,13 +10060,13 @@
         <v>-0.12626548268432</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B17" s="9" t="str">
         <f aca="false">IF(B13&lt;=B12,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -9149,12 +10081,12 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -9166,48 +10098,48 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>1.25</v>
@@ -9250,7 +10182,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>8.75</v>
@@ -9293,7 +10225,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>0.25</v>
@@ -9336,7 +10268,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>0.5</v>
@@ -9379,7 +10311,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>1.25</v>
@@ -9422,7 +10354,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>1.25</v>
@@ -9465,7 +10397,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>0.25</v>
@@ -9508,7 +10440,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>0.25</v>
@@ -9551,7 +10483,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9" t="str">
         <f aca="false">SUMPRODUCT(--(B21:K21&lt;B22:K22))&amp;" / "&amp;SUMPRODUCT(--(B21:K21=B22:K22))&amp;" (共 10)"</f>
@@ -9560,7 +10492,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="9" t="str">
         <f aca="false">SUMPRODUCT(--(B23:K23&lt;B24:K24))&amp;" / "&amp;SUMPRODUCT(--(B23:K23=B24:K24))&amp;" (共 10)"</f>
@@ -9569,7 +10501,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B31" s="9" t="str">
         <f aca="false">SUMPRODUCT(--(B25:K25&lt;B26:K26))&amp;" / "&amp;SUMPRODUCT(--(B25:K25=B26:K26))&amp;" (共 10)"</f>
@@ -9578,7 +10510,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" s="9" t="str">
         <f aca="false">SUMPRODUCT(--(B27:K27&lt;B28:K28))&amp;" / "&amp;SUMPRODUCT(--(B27:K27=B28:K28))&amp;" (共 10)"</f>
@@ -9605,7 +10537,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -9615,17 +10547,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -9637,156 +10569,156 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>2.73942673430051</v>
+        <v>2.76189670572929</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.238178760790997</v>
+        <v>0.236729011747258</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>1.97758376560133</v>
+        <v>2.00515247223236</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.151414206765141</v>
+        <v>0.148140356484435</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">IF(B6=0,"",D6/B6-1)</f>
-        <v>-0.278103064104655</v>
+        <v>-0.273994400995207</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1.09143289727408</v>
+        <v>1.10400776974611</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.0974830673067975</v>
+        <v>0.105209847589851</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1.00614878135162</v>
+        <v>0.996639208844457</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0534967852773724</v>
+        <v>0.0553382539210272</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">IF(B7=0,"",D7/B7-1)</f>
-        <v>-0.0781395870836048</v>
+        <v>-0.0972534467998788</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1.60416666666667</v>
+        <v>0.9765625</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1.47054411698527</v>
+        <v>0.612322598671444</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>0.789583333333333</v>
+        <v>0.8515625</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.507534378966916</v>
+        <v>0.478989720499042</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">IF(B8=0,"",D8/B8-1)</f>
-        <v>-0.507792207792208</v>
+        <v>-0.128</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="10" t="n">
-        <v>2.65781293270989</v>
+        <v>2.67921871733148</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.229373210533129</v>
+        <v>0.228425079972053</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1.92889250624194</v>
+        <v>1.95467515661745</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.144789970141345</v>
+        <v>0.1425283745291</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">IF(B9=0,"",D9/B9-1)</f>
-        <v>-0.274255730152066</v>
+        <v>-0.270430911827787</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="10" t="n">
-        <v>2.76959314951954</v>
+        <v>2.79027457863489</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.235862529830526</v>
+        <v>0.235780087533817</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2.02964186697718</v>
+        <v>2.05471571023817</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.146949584306079</v>
+        <v>0.146430029007944</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">IF(B10=0,"",D10/B10-1)</f>
-        <v>-0.267169668104763</v>
+        <v>-0.263615227701564</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass (tol. 5 s)</v>
+        <v>pass</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9" t="str">
@@ -9797,131 +10729,131 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="10" t="n">
-        <v>0.323001736427305</v>
+        <v>0.326203400901427</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.0151267930497383</v>
+        <v>0.0142648931496322</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>0.240540474022652</v>
+        <v>0.240906842439639</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.00728376369051409</v>
+        <v>0.00809614721636847</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">IF(B12=0,"",D12/B12-1)</f>
-        <v>-0.255296653562144</v>
+        <v>-0.261482738150739</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="10" t="n">
-        <v>0.145120742732053</v>
+        <v>0.144468598011641</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0.0116606938127742</v>
+        <v>0.0121172907280408</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>0.14425790431115</v>
+        <v>0.142736857674104</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0104947587311396</v>
+        <v>0.00985464800867554</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">IF(B13=0,"",D13/B13-1)</f>
-        <v>-0.00594565879873499</v>
+        <v>-0.0119869671428358</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="10" t="n">
-        <v>0.177083333333333</v>
+        <v>0.165625</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.0996216802039931</v>
+        <v>0.106571205656125</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.129166666666667</v>
+        <v>0.134375</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.0767164693313415</v>
+        <v>0.0654760213742405</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">IF(B14=0,"",D14/B14-1)</f>
-        <v>-0.270588235294117</v>
+        <v>-0.188679245283019</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="10" t="n">
-        <v>0.314170376581005</v>
+        <v>0.317174222284547</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.0144439798355404</v>
+        <v>0.0137712373527726</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>0.235720652615393</v>
+        <v>0.235998892846067</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.00716402249081583</v>
+        <v>0.00798540832343343</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">IF(B15=0,"",D15/B15-1)</f>
-        <v>-0.249704395491866</v>
+        <v>-0.255932934441485</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>0.328901152222286</v>
+        <v>0.331804254247681</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.0146451476898401</v>
+        <v>0.0142684938105662</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>0.250188020397275</v>
+        <v>0.250335847898947</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.00777152208793024</v>
+        <v>0.0086540438768751</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">IF(B16=0,"",D16/B16-1)</f>
-        <v>-0.239321544765564</v>
+        <v>-0.24553153043035</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B17" s="9" t="str">
         <f aca="false">IF(B13&lt;=B12,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -9936,12 +10868,12 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -9953,48 +10885,42 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>2.5</v>
@@ -10021,23 +10947,17 @@
         <v>0</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0</v>
+        <f aca="false">AVERAGE(B21:I21)</f>
+        <v>1.25</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <f aca="false">AVERAGE(B21:K21)</f>
-        <v>1</v>
-      </c>
-      <c r="M21" s="10" t="n">
-        <f aca="false">STDEV(B21:K21)</f>
-        <v>1.74801474695025</v>
+        <f aca="false">STDEV(B21:I21)</f>
+        <v>1.88982236504614</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>2.5</v>
@@ -10055,32 +10975,26 @@
         <v>0</v>
       </c>
       <c r="G22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="I22" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="J22" s="10" t="n">
-        <v>0</v>
+        <f aca="false">AVERAGE(B22:I22)</f>
+        <v>1.25</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <f aca="false">AVERAGE(B22:K22)</f>
-        <v>1.5</v>
-      </c>
-      <c r="M22" s="10" t="n">
-        <f aca="false">STDEV(B22:K22)</f>
-        <v>1.74801474695025</v>
+        <f aca="false">STDEV(B22:I22)</f>
+        <v>1.88982236504614</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>0.5</v>
@@ -10107,23 +11021,17 @@
         <v>0</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0</v>
+        <f aca="false">AVERAGE(B23:I23)</f>
+        <v>0.1875</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <f aca="false">AVERAGE(B23:K23)</f>
-        <v>0.15</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <f aca="false">STDEV(B23:K23)</f>
-        <v>0.241522945769824</v>
+        <f aca="false">STDEV(B23:I23)</f>
+        <v>0.258774584753383</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>0.5</v>
@@ -10141,32 +11049,26 @@
         <v>0</v>
       </c>
       <c r="G24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="H24" s="18" t="n">
+      <c r="I24" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="10" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J24" s="10" t="n">
-        <v>0</v>
+        <f aca="false">AVERAGE(B24:I24)</f>
+        <v>0.1875</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <f aca="false">AVERAGE(B24:K24)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <f aca="false">STDEV(B24:K24)</f>
-        <v>0.263523138347365</v>
+        <f aca="false">STDEV(B24:I24)</f>
+        <v>0.258774584753383</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>0</v>
@@ -10187,29 +11089,23 @@
         <v>0</v>
       </c>
       <c r="H25" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I25" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="J25" s="10" t="n">
-        <v>0</v>
+        <f aca="false">AVERAGE(B25:I25)</f>
+        <v>0.3125</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <f aca="false">AVERAGE(B25:K25)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <f aca="false">STDEV(B25:K25)</f>
-        <v>0.790569415042095</v>
+        <f aca="false">STDEV(B25:I25)</f>
+        <v>0.883883476483184</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>0</v>
@@ -10233,26 +11129,20 @@
         <v>0</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2.5</v>
+        <f aca="false">AVERAGE(B26:I26)</f>
+        <v>0.3125</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="10" t="n">
-        <f aca="false">AVERAGE(B26:K26)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M26" s="10" t="n">
-        <f aca="false">STDEV(B26:K26)</f>
-        <v>0.790569415042095</v>
+        <f aca="false">STDEV(B26:I26)</f>
+        <v>0.883883476483184</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>0</v>
@@ -10273,29 +11163,23 @@
         <v>0</v>
       </c>
       <c r="H27" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I27" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="10" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J27" s="10" t="n">
-        <v>0</v>
+        <f aca="false">AVERAGE(B27:I27)</f>
+        <v>0.0625</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10" t="n">
-        <f aca="false">AVERAGE(B27:K27)</f>
-        <v>0.05</v>
-      </c>
-      <c r="M27" s="10" t="n">
-        <f aca="false">STDEV(B27:K27)</f>
-        <v>0.158113883008419</v>
+        <f aca="false">STDEV(B27:I27)</f>
+        <v>0.176776695296637</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>0</v>
@@ -10319,393 +11203,714 @@
         <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.5</v>
+        <f aca="false">AVERAGE(B28:I28)</f>
+        <v>0.0625</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="10" t="n">
-        <f aca="false">AVERAGE(B28:K28)</f>
-        <v>0.05</v>
-      </c>
-      <c r="M28" s="10" t="n">
-        <f aca="false">STDEV(B28:K28)</f>
-        <v>0.158113883008419</v>
+        <f aca="false">STDEV(B28:I28)</f>
+        <v>0.176776695296637</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9" t="str">
-        <f aca="false">SUMPRODUCT(--(B21:K21&lt;B22:K22))&amp;" / "&amp;SUMPRODUCT(--(B21:K21=B22:K22))&amp;" (共 10)"</f>
-        <v>4 / 4 (共 10)</v>
+        <f aca="false">SUMPRODUCT(--(B21:I21&lt;B22:I22))&amp;" / "&amp;SUMPRODUCT(--(B21:I21=B22:I22))&amp;" (共 8)"</f>
+        <v>2 / 4 (共 8)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="9" t="str">
-        <f aca="false">SUMPRODUCT(--(B23:K23&lt;B24:K24))&amp;" / "&amp;SUMPRODUCT(--(B23:K23=B24:K24))&amp;" (共 10)"</f>
-        <v>4 / 4 (共 10)</v>
+        <f aca="false">SUMPRODUCT(--(B23:I23&lt;B24:I24))&amp;" / "&amp;SUMPRODUCT(--(B23:I23=B24:I24))&amp;" (共 8)"</f>
+        <v>2 / 4 (共 8)</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B31" s="9" t="str">
-        <f aca="false">SUMPRODUCT(--(B25:K25&lt;B26:K26))&amp;" / "&amp;SUMPRODUCT(--(B25:K25=B26:K26))&amp;" (共 10)"</f>
-        <v>1 / 8 (共 10)</v>
+        <f aca="false">SUMPRODUCT(--(B25:I25&lt;B26:I26))&amp;" / "&amp;SUMPRODUCT(--(B25:I25=B26:I26))&amp;" (共 8)"</f>
+        <v>1 / 6 (共 8)</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" s="9" t="str">
-        <f aca="false">SUMPRODUCT(--(B27:K27&lt;B28:K28))&amp;" / "&amp;SUMPRODUCT(--(B27:K27=B28:K28))&amp;" (共 10)"</f>
-        <v>1 / 8 (共 10)</v>
+        <f aca="false">SUMPRODUCT(--(B27:I27&lt;B28:I28))&amp;" / "&amp;SUMPRODUCT(--(B27:I27=B28:I28))&amp;" (共 8)"</f>
+        <v>1 / 6 (共 8)</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
+      <c r="A34" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="A35" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="B38" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="D38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="E38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="F38" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
+      <c r="G38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="D36" s="17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <f aca="false">IF(B36=0,"",D36/B36-1)</f>
-        <v>-0.507070707070707</v>
-      </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
+      <c r="H38" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D37" s="17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <f aca="false">IF(B37=0,"",D37/B37-1)</f>
-        <v>-0.158730158730159</v>
-      </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <f aca="false">IF(B38=0,"",D38/B38-1)</f>
-        <v>0.0222222222222221</v>
-      </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B39" s="10" t="n">
-        <v>4.75</v>
+        <v>2.73942673430051</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1.17</v>
+        <v>0.238178760790997</v>
       </c>
       <c r="D39" s="17" t="n">
-        <v>2.38</v>
+        <v>1.97758376560133</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.31</v>
+        <v>0.151414206765141</v>
       </c>
       <c r="F39" s="11" t="n">
         <f aca="false">IF(B39=0,"",D39/B39-1)</f>
-        <v>-0.498947368421053</v>
+        <v>-0.278103064104655</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>46</v>
+      <c r="A40" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="B40" s="10" t="n">
-        <v>4.89</v>
+        <v>1.09143289727408</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>1.18</v>
+        <v>0.0974830673067975</v>
       </c>
       <c r="D40" s="17" t="n">
-        <v>2.48</v>
+        <v>1.00614878135162</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.31</v>
+        <v>0.0534967852773724</v>
       </c>
       <c r="F40" s="11" t="n">
         <f aca="false">IF(B40=0,"",D40/B40-1)</f>
-        <v>-0.492842535787321</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>119</v>
-      </c>
+        <v>-0.0781395870836048</v>
+      </c>
+      <c r="G40" s="9"/>
       <c r="H40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="9" t="str">
-        <f aca="false">IF(AND(B38&lt;=B37,B37&lt;=B36),"pass",IF(AND(B38-B37&lt;=5,B37-B36&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9" t="str">
-        <f aca="false">IF(AND(D38&lt;=D37,D37&lt;=D36),"pass",IF(AND(D38-D37&lt;=5,D37-D36&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>1.60416666666667</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>1.47054411698527</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>0.789583333333333</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.507534378966916</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <f aca="false">IF(B41=0,"",D41/B41-1)</f>
+        <v>-0.507792207792208</v>
+      </c>
       <c r="G41" s="9"/>
       <c r="H41" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B42" s="10" t="n">
-        <v>0.57</v>
+        <v>2.65781293270989</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>0.09</v>
+        <v>0.229373210533129</v>
       </c>
       <c r="D42" s="17" t="n">
-        <v>0.27</v>
+        <v>1.92889250624194</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.03</v>
+        <v>0.144789970141345</v>
       </c>
       <c r="F42" s="11" t="n">
         <f aca="false">IF(B42=0,"",D42/B42-1)</f>
-        <v>-0.526315789473684</v>
+        <v>-0.274255730152066</v>
       </c>
       <c r="G42" s="9"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="s">
-        <v>51</v>
+      <c r="A43" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="B43" s="10" t="n">
-        <v>0.18</v>
+        <v>2.76959314951954</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>0.02</v>
+        <v>0.235862529830526</v>
       </c>
       <c r="D43" s="17" t="n">
-        <v>0.15</v>
+        <v>2.02964186697718</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.02</v>
+        <v>0.146949584306079</v>
       </c>
       <c r="F43" s="11" t="n">
         <f aca="false">IF(B43=0,"",D43/B43-1)</f>
-        <v>-0.166666666666667</v>
-      </c>
-      <c r="G43" s="9"/>
+        <v>-0.267169668104763</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="H43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <f aca="false">IF(B44=0,"",D44/B44-1)</f>
-        <v>0.0714285714285714</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B44" s="9" t="str">
+        <f aca="false">IF(AND(B41&lt;=B40,B40&lt;=B39),"pass",IF(AND(B41-B40&lt;=5,B40-B39&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>pass (tol. 5 s)</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9" t="str">
+        <f aca="false">IF(AND(D41&lt;=D40,D40&lt;=D39),"pass",IF(AND(D41-D40&lt;=5,D40-D39&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>pass</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="10" t="n">
-        <v>0.55</v>
+        <v>0.323001736427305</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>0.09</v>
+        <v>0.0151267930497383</v>
       </c>
       <c r="D45" s="17" t="n">
-        <v>0.27</v>
+        <v>0.240540474022652</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.03</v>
+        <v>0.00728376369051409</v>
       </c>
       <c r="F45" s="11" t="n">
         <f aca="false">IF(B45=0,"",D45/B45-1)</f>
-        <v>-0.509090909090909</v>
+        <v>-0.255296653562144</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
-        <v>54</v>
+      <c r="A46" s="16" t="s">
+        <v>53</v>
       </c>
       <c r="B46" s="10" t="n">
-        <v>0.566</v>
+        <v>0.145120742732053</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>0.091</v>
+        <v>0.0116606938127742</v>
       </c>
       <c r="D46" s="17" t="n">
-        <v>0.281</v>
+        <v>0.14425790431115</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.027</v>
+        <v>0.0104947587311396</v>
       </c>
       <c r="F46" s="11" t="n">
         <f aca="false">IF(B46=0,"",D46/B46-1)</f>
-        <v>-0.503533568904594</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>119</v>
-      </c>
+        <v>-0.00594565879873499</v>
+      </c>
+      <c r="G46" s="9"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" s="9" t="str">
-        <f aca="false">IF(B43&lt;=B42,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9" t="str">
-        <f aca="false">IF(D43&lt;=D42,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>0.177083333333333</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>0.0996216802039931</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>0.129166666666667</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0767164693313415</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <f aca="false">IF(B47=0,"",D47/B47-1)</f>
+        <v>-0.270588235294117</v>
+      </c>
       <c r="G47" s="9"/>
       <c r="H47" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>0.314170376581005</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>0.0144439798355404</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0.235720652615393</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.00716402249081583</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <f aca="false">IF(B48=0,"",D48/B48-1)</f>
+        <v>-0.249704395491866</v>
+      </c>
+      <c r="G48" s="9"/>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="10" t="n">
+        <v>0.328901152222286</v>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>0.0146451476898401</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>0.250188020397275</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.00777152208793024</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <f aca="false">IF(B49=0,"",D49/B49-1)</f>
+        <v>-0.239321544765564</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="9" t="str">
+        <f aca="false">IF(B46&lt;=B45,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9" t="str">
+        <f aca="false">IF(D46&lt;=D45,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
+      </c>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <f aca="false">IF(B54=0,"",D54/B54-1)</f>
+        <v>-0.507070707070707</v>
+      </c>
+      <c r="G54" s="9"/>
+      <c r="H54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <f aca="false">IF(B55=0,"",D55/B55-1)</f>
+        <v>-0.158730158730159</v>
+      </c>
+      <c r="G55" s="9"/>
+      <c r="H55" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <f aca="false">IF(B56=0,"",D56/B56-1)</f>
+        <v>0.0222222222222221</v>
+      </c>
+      <c r="G56" s="9"/>
+      <c r="H56" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <f aca="false">IF(B57=0,"",D57/B57-1)</f>
+        <v>-0.498947368421053</v>
+      </c>
+      <c r="G57" s="9"/>
+      <c r="H57" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <f aca="false">IF(B58=0,"",D58/B58-1)</f>
+        <v>-0.492842535787321</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="H58" s="8"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="9" t="str">
+        <f aca="false">IF(AND(B56&lt;=B55,B55&lt;=B54),"pass",IF(AND(B56-B55&lt;=5,B55-B54&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>pass</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9" t="str">
+        <f aca="false">IF(AND(D56&lt;=D55,D55&lt;=D54),"pass",IF(AND(D56-D55&lt;=5,D55-D54&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>pass</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <f aca="false">IF(B60=0,"",D60/B60-1)</f>
+        <v>-0.526315789473684</v>
+      </c>
+      <c r="G60" s="9"/>
+      <c r="H60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <f aca="false">IF(B61=0,"",D61/B61-1)</f>
+        <v>-0.166666666666667</v>
+      </c>
+      <c r="G61" s="9"/>
+      <c r="H61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <f aca="false">IF(B62=0,"",D62/B62-1)</f>
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="G62" s="9"/>
+      <c r="H62" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D63" s="17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <f aca="false">IF(B63=0,"",D63/B63-1)</f>
+        <v>-0.509090909090909</v>
+      </c>
+      <c r="G63" s="9"/>
+      <c r="H63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0.566</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <f aca="false">IF(B64=0,"",D64/B64-1)</f>
+        <v>-0.503533568904594</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="9" t="str">
+        <f aca="false">IF(B61&lt;=B60,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
+      </c>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9" t="str">
+        <f aca="false">IF(D61&lt;=D60,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A66:H66"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/experiments/analysis/tables/main_comparison_tables_2026-09-30.xlsx
+++ b/experiments/analysis/tables/main_comparison_tables_2026-09-30.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="157">
   <si>
     <t xml:space="preserve">Main comparison tables - 8STD (standard-phase template + DQN) vs GS-ENUM (enumerated phase sets + FRAP) - 2026-09-30</t>
   </si>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Dublin 11h: the primary block is the USER-SELECTED protocol - seeds 128 and 132 removed from both arms, because in those two seeds the 8STD ambulance amb_0 was caught for 45 s / 90 s at junction 389281 by the Aungier Street right-turn queue spilling back from the unsignalised yield junction (an exogenous bottleneck outside the control set). The full 10-seed result is kept as a reference block; both appear in the Overview.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dublin 18h: PRIMARY block has three arms - 8STD (exp298 ep200), GS (exp300 ep145: split-slot net only) and GS-2 (exp301 ep95: exp300 + since-green observation + log-scale waiting + pressure-anchored phase score + TD-target floor -50); computed from the raw per-seed collector json with the same formulas as the PNG tables. Reference blocks below it: two-arm rerouted v2 (177 cars/h leave at the end of the Aungier approach instead of turning into Peter's Row; GS uses the split-slot enumerated net), best checkpoints exp298 ep200 (8STD, training stopped at ep253) vs exp300 ep145 (GS, training still running) - a snapshot, not a final result. A USER-SELECTED 5-seed block (seeds with zero ambulance stops in both arms) and the original-scenario blocks (exp289/290, 7 of 10 seeds anomalous by the &gt;100 s rule) are kept as reference.</t>
+    <t xml:space="preserve">Dublin 18h: PRIMARY block = rerouted scenario v2 (177 cars/h leave at the end of the Aungier approach instead of turning into Peter's Row), 8STD exp298 ep200 (training stopped at ep253) vs GS-ENUM exp301 ep95 (split-slot enumerated net + since-green observation + log-scale waiting + pressure-anchored phase score + TD-target floor -50; training still running) - a snapshot, not a final result; computed from the raw per-seed collector json with the same formulas as the PNG tables. Reference blocks: original 18h scenario exp289/290 (7 of 10 seeds anomalous by the &gt;100 s rule).</t>
   </si>
   <si>
     <t xml:space="preserve">Source files and generator: experiments/tools/figures/build_main_comparison_xlsx_2026-09-30.py; json paths are on line 2 of each sheet.</t>
@@ -127,10 +127,7 @@
     <t xml:space="preserve">B</t>
   </si>
   <si>
-    <t xml:space="preserve">Dublin 18h: Dublin 18:00, rerouted scenario v2, best checkpoints x 10 seeds, two arms (8STD: exp298 ep200, GS-ENUM: exp300 ep145); anomaly rule (&gt;100 s): no hits  [reference: same data as the PNG]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18h: Dublin 18:00, rerouted scenario v2, 5 seeds with zero ambulance stops in both arms (123, 126, 128, 131, 132)  [USER-SELECTED]</t>
+    <t xml:space="preserve">Dublin 18h: Dublin 18:00 rerouted v2, best checkpoints x 10 seeds (8STD exp298 ep200, GS exp301 ep95) [PRIMARY]</t>
   </si>
   <si>
     <t xml:space="preserve">Dublin 18h: Dublin 18:00, ORIGINAL scenario, best checkpoints x 10 seeds (8STD: exp289 ep270, GS-ENUM: exp290 ep75)  [reference]</t>
@@ -139,42 +136,6 @@
     <t xml:space="preserve">Dublin 18h: Dublin 18:00, ORIGINAL scenario, excl. 7 anomalous seeds (any junction &gt; 100 s in either arm: 124, 125, 127, 128, 130, 131, 132), 3 seeds  [reference]</t>
   </si>
   <si>
-    <t xml:space="preserve">Dublin 18h three-arm block (8STD | GS exp300 | GS-2 exp301): all-class stopped time / visit and J(531)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8STD all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS vs 8STD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 vs 8STD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8STD J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 wins (J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18:00 rerouted v2, three arms, 10 seeds [PRIMARY]</t>
-  </si>
-  <si>
     <t xml:space="preserve">1x1: best checkpoints x 10 evaluation seeds (123, 124, 125, 126, 127, 128, 129, 130, 131, 132); Protocol A</t>
   </si>
   <si>
@@ -460,127 +421,58 @@
     <t xml:space="preserve">Constants from plot_main_table_en_2026-09-22.py (S/EV) = the 11h block of main_comparison_8std_vs_frap_2026-09-22_en.png; 'GS wins 40/40' = J better in all 40 evaluations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dublin 18h: rerouted scenario v2 (177 cars/h leave at the Aungier approach end); GS arms on the split-slot enumerated net; SNAPSHOT (exp300 / exp301 still training)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS = exp300 (split-slot net, no other change); GS-2 = exp301 = exp300 + since-green observation + log-scale waiting + pressure-anchored phase score + TD-target floor -50. Best checkpoints frozen 2026-09-30 evening: 8STD exp298 ep200, GS exp300 ep145, GS-2 exp301 ep95.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18:00 rerouted v2, best checkpoints x 10 seeds, three arms  [PRIMARY, snapshot]; seeds 123, 124, 125, 126, 127, 128, 129, 130, 131, 132; anomaly rule (any junction &gt; 100 s in any arm): no hits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) s.d.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) s.d.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) vs 8STD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) vs 8STD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) vs GS (exp300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) wins vs 8STD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) wins vs 8STD</t>
+    <t xml:space="preserve">Dublin 18h: rerouted scenario v2 (177 cars/h leave at the Aungier approach end); GS on the split-slot enumerated net; SNAPSHOT (exp301 still training)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS = exp301 = split-slot net + since-green observation + log-scale waiting + pressure-anchored phase score + TD-target floor -50. Best checkpoints frozen 2026-09-30 evening: 8STD exp298 ep200 (training stopped at ep253), GS exp301 ep95.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dublin 18:00 rerouted v2, best checkpoints x 10 seeds (8STD: exp298 ep200, GS-ENUM: exp301 ep95)  [PRIMARY, snapshot]; seeds 123, 124, 125, 126, 127, 128, 129, 130, 131, 132; anomaly rule (any junction &gt; 100 s in any arm): no hits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) s.d.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) vs 8STD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) wins vs 8STD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/10 (ties 0)</t>
   </si>
   <si>
     <t xml:space="preserve">0/10 (ties 0)</t>
   </si>
   <si>
-    <t xml:space="preserve">10/10 (ties 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/10 (ties 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/10 (ties 5)</t>
-  </si>
-  <si>
     <t xml:space="preserve">3/10 (ties 5)</t>
   </si>
   <si>
     <t xml:space="preserve">1 ambulance per evaluation (probe route); do not cite the mean alone</t>
   </si>
   <si>
-    <t xml:space="preserve">8/10 (ties 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/10 (ties 8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18:00 rerouted v2, best checkpoints x 10 seeds, three arms  [PRIMARY, snapshot]: same route &amp; departure time, ambulance vs bus probe, 10 seeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) - ambulance (probe route) - Stopped time / visit (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) - bus (same route &amp; time) - Stopped time / visit (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) - ambulance (probe route) - Stop events / visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) - bus (same route &amp; time) - Stop events / visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) - ambulance (probe route) - Stopped time / visit (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) - bus (same route &amp; time) - Stopped time / visit (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) - ambulance (probe route) - Stop events / visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) - bus (same route &amp; time) - Stop events / visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) - stopped time: evaluations with ambulance &lt; bus / ties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS (exp300) - stop events: evaluations with ambulance &lt; bus / ties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) - stopped time: evaluations with ambulance &lt; bus / ties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GS-2 (exp301) - stop events: evaluations with ambulance &lt; bus / ties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18h: best checkpoints x 10 evaluation seeds (123, 124, 125, 126, 127, 128, 129, 130, 131, 132); Protocol A; rerouted scenario v2 (Aungier right-turn cars leave at the approach end), GS on the split-slot enumerated net; SNAPSHOT: exp300 still training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: experiments/analysis/figures/main_comparison_18h_best10seeds_reroute_v2_2026-09-30_en.json (same data as the PNG of that name); anomalous seeds (symmetric rule): none; Tukey outlier seeds: none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18:00, rerouted scenario v2, best checkpoints x 10 seeds, two arms (8STD: exp298 ep200, GS-ENUM: exp300 ep145); anomaly rule (&gt;100 s): no hits  [reference: same data as the PNG]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18:00 rerouted v2: same route &amp; departure time, ambulance vs bus probe, best checkpoints, 10 seeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18h: best checkpoints x 5 evaluation seeds (123, 126, 128, 131, 132); Protocol A, USER-SELECTED: 5 seeds with zero ambulance stops in both arms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: experiments/analysis/figures/main_comparison_18h_best10seeds_reroute_v2_SELECTED_ambzero5_2026-09-30_en.json (same data as the PNG of that name); anomalous seeds (symmetric rule): none; Tukey outlier seeds: none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dublin 18:00, rerouted scenario v2, 5 seeds with zero ambulance stops in both arms (123, 126, 128, 131, 132)  [USER-SELECTED]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0/5</t>
+    <t xml:space="preserve">Dublin 18:00 rerouted v2, best checkpoints x 10 seeds (8STD: exp298 ep200, GS-ENUM: exp301 ep95)  [PRIMARY, snapshot]: same route &amp; departure time, ambulance vs bus probe, 10 seeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) - ambulance (probe route) - Stopped time / visit (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) - bus (same route &amp; time) - Stopped time / visit (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) - ambulance (probe route) - Stop events / visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) - bus (same route &amp; time) - Stop events / visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) - stopped time: evaluations with ambulance &lt; bus / ties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS-ENUM (exp301) - stop events: evaluations with ambulance &lt; bus / ties</t>
   </si>
   <si>
     <t xml:space="preserve">Dublin 18h: best checkpoints x 10 evaluation seeds (123, 124, 125, 126, 127, 128, 129, 130, 131, 132); Protocol A, ORIGINAL 18h scenario (exogenous Aungier/Peter's Row yield lock present), best checkpoints exp289 ep270 / exp290 ep75 (reference)</t>
@@ -784,10 +676,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -798,6 +686,10 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -966,7 +858,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1330,40 +1222,40 @@
         <v>25</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B49</f>
+        <f aca="false">'Dublin 18h'!B9</f>
         <v>3.60388839569416</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D49</f>
-        <v>5.68308025928241</v>
+        <f aca="false">'Dublin 18h'!D9</f>
+        <v>3.05216444071164</v>
       </c>
       <c r="E10" s="8" t="n">
         <f aca="false">IF(C10=0,"",D10/C10-1)</f>
-        <v>0.57693014746861</v>
+        <v>-0.153091298732144</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B50</f>
+        <f aca="false">'Dublin 18h'!B10</f>
         <v>3.7211635599533</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D50</f>
-        <v>5.81875981677413</v>
+        <f aca="false">'Dublin 18h'!D10</f>
+        <v>3.18882418536163</v>
       </c>
       <c r="H10" s="9" t="n">
         <f aca="false">IF(F10=0,"",G10/F10-1)</f>
-        <v>0.563693646631095</v>
+        <v>-0.143057236268957</v>
       </c>
       <c r="I10" s="6" t="str">
-        <f aca="false">'Dublin 18h'!G50</f>
-        <v>0/10</v>
+        <f aca="false">'Dublin 18h'!G10</f>
+        <v>10/10</v>
       </c>
       <c r="J10" s="6" t="str">
-        <f aca="false">'Dublin 18h'!B51</f>
+        <f aca="false">'Dublin 18h'!B11</f>
         <v>pass</v>
       </c>
       <c r="K10" s="6" t="str">
-        <f aca="false">'Dublin 18h'!D51</f>
-        <v>pass (tol. 5 s)</v>
+        <f aca="false">'Dublin 18h'!D11</f>
+        <v>pass</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1374,40 +1266,40 @@
         <v>25</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B83</f>
-        <v>3.57058104695067</v>
+        <f aca="false">'Dublin 18h'!B43</f>
+        <v>16.2028073110655</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D83</f>
-        <v>5.69847219496105</v>
+        <f aca="false">'Dublin 18h'!D43</f>
+        <v>16.550201957309</v>
       </c>
       <c r="E11" s="8" t="n">
         <f aca="false">IF(C11=0,"",D11/C11-1)</f>
-        <v>0.595950944686616</v>
+        <v>0.021440398541694</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B84</f>
-        <v>3.68644022817255</v>
+        <f aca="false">'Dublin 18h'!B44</f>
+        <v>17.0011187356766</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D84</f>
-        <v>5.8267038914822</v>
+        <f aca="false">'Dublin 18h'!D44</f>
+        <v>17.2651837725786</v>
       </c>
       <c r="H11" s="9" t="n">
         <f aca="false">IF(F11=0,"",G11/F11-1)</f>
-        <v>0.580577340425405</v>
+        <v>0.0155322153210906</v>
       </c>
       <c r="I11" s="6" t="str">
-        <f aca="false">'Dublin 18h'!G84</f>
-        <v>0/5</v>
+        <f aca="false">'Dublin 18h'!G44</f>
+        <v>4/10</v>
       </c>
       <c r="J11" s="6" t="str">
-        <f aca="false">'Dublin 18h'!B85</f>
-        <v>pass</v>
+        <f aca="false">'Dublin 18h'!B45</f>
+        <v>fail</v>
       </c>
       <c r="K11" s="6" t="str">
-        <f aca="false">'Dublin 18h'!D85</f>
-        <v>pass</v>
+        <f aca="false">'Dublin 18h'!D45</f>
+        <v>fail</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1418,175 +1310,40 @@
         <v>25</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B102</f>
-        <v>16.2028073110655</v>
+        <f aca="false">'Dublin 18h'!B58</f>
+        <v>15.3494260371416</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D102</f>
-        <v>16.550201957309</v>
+        <f aca="false">'Dublin 18h'!D58</f>
+        <v>13.2976366987359</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">IF(C12=0,"",D12/C12-1)</f>
-        <v>0.021440398541694</v>
+        <v>-0.133672056104306</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B103</f>
-        <v>17.0011187356766</v>
+        <f aca="false">'Dublin 18h'!B59</f>
+        <v>16.0787040385087</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D103</f>
-        <v>17.2651837725786</v>
+        <f aca="false">'Dublin 18h'!D59</f>
+        <v>13.759763195124</v>
       </c>
       <c r="H12" s="9" t="n">
         <f aca="false">IF(F12=0,"",G12/F12-1)</f>
-        <v>0.0155322153210906</v>
+        <v>-0.144224362724185</v>
       </c>
       <c r="I12" s="6" t="str">
-        <f aca="false">'Dublin 18h'!G103</f>
-        <v>4/10</v>
+        <f aca="false">'Dublin 18h'!G59</f>
+        <v>2/3</v>
       </c>
       <c r="J12" s="6" t="str">
-        <f aca="false">'Dublin 18h'!B104</f>
-        <v>fail</v>
+        <f aca="false">'Dublin 18h'!B60</f>
+        <v>pass</v>
       </c>
       <c r="K12" s="6" t="str">
-        <f aca="false">'Dublin 18h'!D104</f>
-        <v>fail</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B117</f>
-        <v>15.3494260371416</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D117</f>
-        <v>13.2976366987359</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <f aca="false">IF(C13=0,"",D13/C13-1)</f>
-        <v>-0.133672056104306</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B118</f>
-        <v>16.0787040385087</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D118</f>
-        <v>13.759763195124</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <f aca="false">IF(F13=0,"",G13/F13-1)</f>
-        <v>-0.144224362724185</v>
-      </c>
-      <c r="I13" s="6" t="str">
-        <f aca="false">'Dublin 18h'!G118</f>
-        <v>2/3</v>
-      </c>
-      <c r="J13" s="6" t="str">
-        <f aca="false">'Dublin 18h'!B119</f>
+        <f aca="false">'Dublin 18h'!D60</f>
         <v>pass</v>
-      </c>
-      <c r="K13" s="6" t="str">
-        <f aca="false">'Dublin 18h'!D119</f>
-        <v>pass</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <f aca="false">'Dublin 18h'!B9</f>
-        <v>3.60388839569416</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D9</f>
-        <v>5.68308025928241</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <f aca="false">'Dublin 18h'!F9</f>
-        <v>3.05216444071164</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <f aca="false">IF(C17=0,"",D17/C17-1)</f>
-        <v>0.57693014746861</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <f aca="false">IF(C17=0,"",E17/C17-1)</f>
-        <v>-0.153091298732144</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <f aca="false">'Dublin 18h'!B10</f>
-        <v>3.7211635599533</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <f aca="false">'Dublin 18h'!D10</f>
-        <v>5.81875981677413</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <f aca="false">'Dublin 18h'!F10</f>
-        <v>3.18882418536163</v>
-      </c>
-      <c r="K17" s="6" t="str">
-        <f aca="false">'Dublin 18h'!K10</f>
-        <v>0/10</v>
-      </c>
-      <c r="L17" s="6" t="str">
-        <f aca="false">'Dublin 18h'!L10</f>
-        <v>10/10</v>
       </c>
     </row>
   </sheetData>
@@ -1615,57 +1372,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>50</v>
+      <c r="A2" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>32.2318059299191</v>
       </c>
       <c r="C6" s="7" t="n">
@@ -1686,9 +1443,9 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>6.7625</v>
       </c>
       <c r="C7" s="7" t="n">
@@ -1709,9 +1466,9 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>4.25</v>
       </c>
       <c r="C8" s="7" t="n">
@@ -1729,14 +1486,14 @@
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>30.8662898334041</v>
       </c>
       <c r="C9" s="7" t="n">
@@ -1757,9 +1514,9 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>31.809305222372</v>
       </c>
       <c r="C10" s="7" t="n">
@@ -1776,13 +1533,13 @@
         <v>0.0816927561102245</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -1797,14 +1554,14 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B12" s="12" t="n">
         <v>1.12789757412399</v>
       </c>
       <c r="C12" s="7" t="n">
@@ -1825,7 +1582,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>0.8325</v>
@@ -1833,7 +1590,7 @@
       <c r="C13" s="7" t="n">
         <v>0.0851836251870041</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>0.77</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -1848,9 +1605,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B14" s="12" t="n">
         <v>0.533333333333333</v>
       </c>
       <c r="C14" s="7" t="n">
@@ -1868,14 +1625,14 @@
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B15" s="12" t="n">
         <v>1.11162989392257</v>
       </c>
       <c r="C15" s="7" t="n">
@@ -1896,9 +1653,9 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B16" s="12" t="n">
         <v>1.17537199236298</v>
       </c>
       <c r="C16" s="7" t="n">
@@ -1915,13 +1672,13 @@
         <v>0.0793823066215862</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B17" s="6" t="str">
         <f aca="false">IF(AND(B14&lt;=B13,B13&lt;=B12),"pass",IF(AND(B14-B13&lt;=0.5,B13-B12&lt;=0.5),"pass (tol.)","fail"))</f>
@@ -1938,48 +1695,48 @@
       <c r="H17" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B21" s="12" t="n">
         <v>31.7303084755915</v>
       </c>
       <c r="C21" s="7" t="n">
@@ -2000,9 +1757,9 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B22" s="12" t="n">
         <v>6.75</v>
       </c>
       <c r="C22" s="7" t="n">
@@ -2023,9 +1780,9 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B23" s="12" t="n">
         <v>3.98148148148148</v>
       </c>
       <c r="C23" s="7" t="n">
@@ -2043,14 +1800,14 @@
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B24" s="12" t="n">
         <v>30.3949575643627</v>
       </c>
       <c r="C24" s="7" t="n">
@@ -2071,9 +1828,9 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B25" s="12" t="n">
         <v>31.3218402715384</v>
       </c>
       <c r="C25" s="7" t="n">
@@ -2090,13 +1847,13 @@
         <v>0.112700369720723</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B26" s="6" t="str">
         <f aca="false">IF(AND(B23&lt;=B22,B22&lt;=B21),"pass",IF(AND(B23-B22&lt;=5,B22-B21&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -2111,14 +1868,14 @@
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B27" s="12" t="n">
         <v>1.12144354597185</v>
       </c>
       <c r="C27" s="7" t="n">
@@ -2139,7 +1896,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>0.830555555555555</v>
@@ -2147,7 +1904,7 @@
       <c r="C28" s="7" t="n">
         <v>0.0895806416477616</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="12" t="n">
         <v>0.775</v>
       </c>
       <c r="E28" s="7" t="n">
@@ -2162,9 +1919,9 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B29" s="12" t="n">
         <v>0.481481481481482</v>
       </c>
       <c r="C29" s="7" t="n">
@@ -2182,14 +1939,14 @@
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B30" s="12" t="n">
         <v>1.10534956366486</v>
       </c>
       <c r="C30" s="7" t="n">
@@ -2210,9 +1967,9 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B31" s="12" t="n">
         <v>1.16851061445543</v>
       </c>
       <c r="C31" s="7" t="n">
@@ -2229,13 +1986,13 @@
         <v>0.0954842192013747</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B32" s="6" t="str">
         <f aca="false">IF(AND(B29&lt;=B28,B28&lt;=B27),"pass",IF(AND(B29-B28&lt;=0.5,B28-B27&lt;=0.5),"pass (tol.)","fail"))</f>
@@ -2252,61 +2009,61 @@
       <c r="H32" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
+      <c r="A34" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>31.7587601078167</v>
@@ -2326,7 +2083,7 @@
       <c r="G36" s="7" t="n">
         <v>36.7452830188679</v>
       </c>
-      <c r="H36" s="10" t="n">
+      <c r="H36" s="13" t="n">
         <v>32.5134770889488</v>
       </c>
       <c r="I36" s="7" t="n">
@@ -2349,7 +2106,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>1.0633423180593</v>
@@ -2369,7 +2126,7 @@
       <c r="G37" s="7" t="n">
         <v>1.18598382749326</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="H37" s="13" t="n">
         <v>1.13342318059299</v>
       </c>
       <c r="I37" s="7" t="n">
@@ -2392,7 +2149,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>5.5</v>
@@ -2412,7 +2169,7 @@
       <c r="G38" s="7" t="n">
         <v>6.875</v>
       </c>
-      <c r="H38" s="10" t="n">
+      <c r="H38" s="13" t="n">
         <v>7.5</v>
       </c>
       <c r="I38" s="7" t="n">
@@ -2435,7 +2192,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>0.675</v>
@@ -2455,7 +2212,7 @@
       <c r="G39" s="7" t="n">
         <v>0.85</v>
       </c>
-      <c r="H39" s="10" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.775</v>
       </c>
       <c r="I39" s="7" t="n">
@@ -2478,7 +2235,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>5</v>
@@ -2498,7 +2255,7 @@
       <c r="G40" s="7" t="n">
         <v>6.66666666666667</v>
       </c>
-      <c r="H40" s="10" t="n">
+      <c r="H40" s="13" t="n">
         <v>7.5</v>
       </c>
       <c r="I40" s="7" t="n">
@@ -2521,7 +2278,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>0.5</v>
@@ -2541,7 +2298,7 @@
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="10" t="n">
+      <c r="H41" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="7" t="n">
@@ -2564,7 +2321,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>30.3507653061224</v>
@@ -2584,7 +2341,7 @@
       <c r="G42" s="7" t="n">
         <v>35.1082802547771</v>
       </c>
-      <c r="H42" s="10" t="n">
+      <c r="H42" s="13" t="n">
         <v>31.1734693877551</v>
       </c>
       <c r="I42" s="7" t="n">
@@ -2607,7 +2364,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>1.04209183673469</v>
@@ -2627,7 +2384,7 @@
       <c r="G43" s="7" t="n">
         <v>1.16815286624204</v>
       </c>
-      <c r="H43" s="10" t="n">
+      <c r="H43" s="13" t="n">
         <v>1.11479591836735</v>
       </c>
       <c r="I43" s="7" t="n">
@@ -2650,7 +2407,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>32.243935309973</v>
@@ -2670,7 +2427,7 @@
       <c r="G44" s="7" t="n">
         <v>30.7277628032345</v>
       </c>
-      <c r="H44" s="10" t="n">
+      <c r="H44" s="13" t="n">
         <v>33.4905660377359</v>
       </c>
       <c r="I44" s="7" t="n">
@@ -2693,7 +2450,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B45" s="7" t="n">
         <v>1.17250673854447</v>
@@ -2713,7 +2470,7 @@
       <c r="G45" s="7" t="n">
         <v>1.12803234501348</v>
       </c>
-      <c r="H45" s="10" t="n">
+      <c r="H45" s="13" t="n">
         <v>1.22102425876011</v>
       </c>
       <c r="I45" s="7" t="n">
@@ -2736,7 +2493,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>6.125</v>
@@ -2756,7 +2513,7 @@
       <c r="G46" s="7" t="n">
         <v>7.25</v>
       </c>
-      <c r="H46" s="10" t="n">
+      <c r="H46" s="13" t="n">
         <v>7.375</v>
       </c>
       <c r="I46" s="7" t="n">
@@ -2779,7 +2536,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>0.65</v>
@@ -2799,7 +2556,7 @@
       <c r="G47" s="7" t="n">
         <v>0.725</v>
       </c>
-      <c r="H47" s="10" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.775</v>
       </c>
       <c r="I47" s="7" t="n">
@@ -2822,7 +2579,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>7.5</v>
@@ -2842,7 +2599,7 @@
       <c r="G48" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="10" t="n">
+      <c r="H48" s="13" t="n">
         <v>5</v>
       </c>
       <c r="I48" s="7" t="n">
@@ -2865,7 +2622,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>0.5</v>
@@ -2885,7 +2642,7 @@
       <c r="G49" s="7" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="H49" s="10" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="I49" s="7" t="n">
@@ -2908,7 +2665,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>30.8482142857143</v>
@@ -2928,7 +2685,7 @@
       <c r="G50" s="7" t="n">
         <v>29.4331210191083</v>
       </c>
-      <c r="H50" s="10" t="n">
+      <c r="H50" s="13" t="n">
         <v>32.0854591836735</v>
       </c>
       <c r="I50" s="7" t="n">
@@ -2951,7 +2708,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B51" s="7" t="n">
         <v>1.14413265306123</v>
@@ -2971,7 +2728,7 @@
       <c r="G51" s="7" t="n">
         <v>1.10573248407643</v>
       </c>
-      <c r="H51" s="10" t="n">
+      <c r="H51" s="13" t="n">
         <v>1.19642857142857</v>
       </c>
       <c r="I51" s="7" t="n">
@@ -3023,57 +2780,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>108</v>
+      <c r="A2" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>25.3515894955079</v>
       </c>
       <c r="C6" s="7" t="n">
@@ -3094,9 +2851,9 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>4.70416666666667</v>
       </c>
       <c r="C7" s="7" t="n">
@@ -3117,9 +2874,9 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>1.74603174603175</v>
       </c>
       <c r="C8" s="7" t="n">
@@ -3137,14 +2894,14 @@
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>23.7536031177601</v>
       </c>
       <c r="C9" s="7" t="n">
@@ -3165,9 +2922,9 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>24.792079465177</v>
       </c>
       <c r="C10" s="7" t="n">
@@ -3184,13 +2941,13 @@
         <v>0.165313174703693</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -3205,14 +2962,14 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B12" s="12" t="n">
         <v>1.02161944252476</v>
       </c>
       <c r="C12" s="7" t="n">
@@ -3233,9 +2990,9 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="B13" s="12" t="n">
         <v>0.624166666666667</v>
       </c>
       <c r="C13" s="7" t="n">
@@ -3256,9 +3013,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B14" s="12" t="n">
         <v>0.285714285714286</v>
       </c>
       <c r="C14" s="7" t="n">
@@ -3276,14 +3033,14 @@
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B15" s="12" t="n">
         <v>0.990637030580086</v>
       </c>
       <c r="C15" s="7" t="n">
@@ -3304,9 +3061,9 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B16" s="12" t="n">
         <v>1.06456347039853</v>
       </c>
       <c r="C16" s="7" t="n">
@@ -3323,13 +3080,13 @@
         <v>0.0944559589258516</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B17" s="6" t="str">
         <f aca="false">IF(AND(B14&lt;=B13,B13&lt;=B12),"pass",IF(AND(B14-B13&lt;=0.5,B13-B12&lt;=0.5),"pass (tol.)","fail"))</f>
@@ -3346,61 +3103,61 @@
       <c r="H17" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>24.4874452891039</v>
@@ -3420,7 +3177,7 @@
       <c r="G21" s="7" t="n">
         <v>24.9285878829763</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" s="13" t="n">
         <v>26.4990785533287</v>
       </c>
       <c r="I21" s="7" t="n">
@@ -3443,7 +3200,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>1.00714121170237</v>
@@ -3463,7 +3220,7 @@
       <c r="G22" s="7" t="n">
         <v>1.00852338170928</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="13" t="n">
         <v>1.04250172771251</v>
       </c>
       <c r="I22" s="7" t="n">
@@ -3486,7 +3243,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>4.45833333333333</v>
@@ -3506,7 +3263,7 @@
       <c r="G23" s="7" t="n">
         <v>5.5</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="13" t="n">
         <v>5.04166666666667</v>
       </c>
       <c r="I23" s="7" t="n">
@@ -3529,7 +3286,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>0.575</v>
@@ -3549,7 +3306,7 @@
       <c r="G24" s="7" t="n">
         <v>0.675</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.691666666666667</v>
       </c>
       <c r="I24" s="7" t="n">
@@ -3572,7 +3329,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>0</v>
@@ -3588,7 +3345,7 @@
       <c r="G25" s="7" t="n">
         <v>1.66666666666667</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="13" t="n">
         <v>3.33333333333333</v>
       </c>
       <c r="I25" s="7"/>
@@ -3609,7 +3366,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>0</v>
@@ -3625,7 +3382,7 @@
       <c r="G26" s="7" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="I26" s="7"/>
@@ -3646,7 +3403,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>22.9243679626089</v>
@@ -3666,7 +3423,7 @@
       <c r="G27" s="7" t="n">
         <v>23.4130019120459</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="13" t="n">
         <v>24.8421556122449</v>
       </c>
       <c r="I27" s="7" t="n">
@@ -3689,7 +3446,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>0.972806458466114</v>
@@ -3709,7 +3466,7 @@
       <c r="G28" s="7" t="n">
         <v>0.982154238368388</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="13" t="n">
         <v>1.01541241496599</v>
       </c>
       <c r="I28" s="7" t="n">
@@ -3732,7 +3489,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>29.7800046072334</v>
@@ -3752,7 +3509,7 @@
       <c r="G29" s="7" t="n">
         <v>29.0699147661829</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H29" s="13" t="n">
         <v>28.1536512324349</v>
       </c>
       <c r="I29" s="7" t="n">
@@ -3775,7 +3532,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>1.11161022805805</v>
@@ -3795,7 +3552,7 @@
       <c r="G30" s="7" t="n">
         <v>1.09548491131076</v>
       </c>
-      <c r="H30" s="10" t="n">
+      <c r="H30" s="13" t="n">
         <v>1.06381018198572</v>
       </c>
       <c r="I30" s="7" t="n">
@@ -3818,7 +3575,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>8.54166666666667</v>
@@ -3838,7 +3595,7 @@
       <c r="G31" s="7" t="n">
         <v>7.375</v>
       </c>
-      <c r="H31" s="10" t="n">
+      <c r="H31" s="13" t="n">
         <v>7.625</v>
       </c>
       <c r="I31" s="7" t="n">
@@ -3861,7 +3618,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>0.883333333333333</v>
@@ -3881,7 +3638,7 @@
       <c r="G32" s="7" t="n">
         <v>0.825</v>
       </c>
-      <c r="H32" s="10" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.8</v>
       </c>
       <c r="I32" s="7" t="n">
@@ -3904,7 +3661,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>6.66666666666667</v>
@@ -3920,7 +3677,7 @@
       <c r="G33" s="7" t="n">
         <v>4.16666666666667</v>
       </c>
-      <c r="H33" s="10" t="n">
+      <c r="H33" s="13" t="n">
         <v>6.66666666666667</v>
       </c>
       <c r="I33" s="7"/>
@@ -3941,7 +3698,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>0.666666666666667</v>
@@ -3957,7 +3714,7 @@
       <c r="G34" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="H34" s="10" t="n">
+      <c r="H34" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="7"/>
@@ -3978,7 +3735,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>28.1261950286807</v>
@@ -3998,7 +3755,7 @@
       <c r="G35" s="7" t="n">
         <v>27.3789037603569</v>
       </c>
-      <c r="H35" s="10" t="n">
+      <c r="H35" s="13" t="n">
         <v>26.5688775510204</v>
       </c>
       <c r="I35" s="7" t="n">
@@ -4021,7 +3778,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>1.09358402379435</v>
@@ -4041,7 +3798,7 @@
       <c r="G36" s="7" t="n">
         <v>1.07403866581687</v>
       </c>
-      <c r="H36" s="10" t="n">
+      <c r="H36" s="13" t="n">
         <v>1.04357993197279</v>
       </c>
       <c r="I36" s="7" t="n">
@@ -4092,55 +3849,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>113</v>
+      <c r="A2" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>0.764315207480353</v>
@@ -4148,7 +3905,7 @@
       <c r="C6" s="7" t="n">
         <v>0.0583731693603074</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>0.661055365357199</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -4163,7 +3920,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>0.399404761904762</v>
@@ -4171,7 +3928,7 @@
       <c r="C7" s="7" t="n">
         <v>0.176123096833139</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.3625</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -4186,7 +3943,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.375</v>
@@ -4194,7 +3951,7 @@
       <c r="C8" s="7" t="n">
         <v>0.57282196186948</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -4206,12 +3963,12 @@
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.759914434999951</v>
@@ -4219,7 +3976,7 @@
       <c r="C9" s="7" t="n">
         <v>0.0567901248988525</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.657314845890638</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -4234,7 +3991,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.770377529184126</v>
@@ -4242,7 +3999,7 @@
       <c r="C10" s="7" t="n">
         <v>0.0552364028407932</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.666410345436376</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -4253,13 +4010,13 @@
         <v>-0.134956147874481</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -4274,12 +4031,12 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>0.10846497828997</v>
@@ -4287,7 +4044,7 @@
       <c r="C12" s="7" t="n">
         <v>0.00740925418414015</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <v>0.0946555009254376</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -4302,7 +4059,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>0.0602380952380952</v>
@@ -4310,7 +4067,7 @@
       <c r="C13" s="7" t="n">
         <v>0.0228819310033028</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>0.0589285714285714</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -4325,7 +4082,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>0.075</v>
@@ -4333,7 +4090,7 @@
       <c r="C14" s="7" t="n">
         <v>0.114564392373896</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>0.05</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -4345,12 +4102,12 @@
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>0.107910373615727</v>
@@ -4358,7 +4115,7 @@
       <c r="C15" s="7" t="n">
         <v>0.00717887885125108</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="12" t="n">
         <v>0.0942146537936148</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -4373,7 +4130,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>0.109572337766947</v>
@@ -4381,7 +4138,7 @@
       <c r="C16" s="7" t="n">
         <v>0.00693391659432518</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>0.0957371336499541</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -4392,13 +4149,13 @@
         <v>-0.12626548268432</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B17" s="6" t="str">
         <f aca="false">IF(B13&lt;=B12,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -4413,65 +4170,65 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="5" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>1.25</v>
@@ -4491,7 +4248,7 @@
       <c r="G21" s="7" t="n">
         <v>1.25</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
@@ -4514,7 +4271,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>8.75</v>
@@ -4534,7 +4291,7 @@
       <c r="G22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="13" t="n">
         <v>1.25</v>
       </c>
       <c r="I22" s="7" t="n">
@@ -4557,7 +4314,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>0.25</v>
@@ -4577,7 +4334,7 @@
       <c r="G23" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
@@ -4600,7 +4357,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>0.5</v>
@@ -4620,7 +4377,7 @@
       <c r="G24" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="I24" s="7" t="n">
@@ -4643,7 +4400,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>1.25</v>
@@ -4663,7 +4420,7 @@
       <c r="G25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
@@ -4686,7 +4443,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>1.25</v>
@@ -4706,7 +4463,7 @@
       <c r="G26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="13" t="n">
         <v>1.25</v>
       </c>
       <c r="I26" s="7" t="n">
@@ -4729,7 +4486,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>0.25</v>
@@ -4749,7 +4506,7 @@
       <c r="G27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
@@ -4772,7 +4529,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>0.25</v>
@@ -4792,7 +4549,7 @@
       <c r="G28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="I28" s="7" t="n">
@@ -4815,7 +4572,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B29" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B21:K21&lt;B22:K22))&amp;" / "&amp;SUMPRODUCT(--(B21:K21=B22:K22))&amp;" (of 10)"</f>
@@ -4824,7 +4581,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B30" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B23:K23&lt;B24:K24))&amp;" / "&amp;SUMPRODUCT(--(B23:K23=B24:K24))&amp;" (of 10)"</f>
@@ -4833,7 +4590,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B31" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B25:K25&lt;B26:K26))&amp;" / "&amp;SUMPRODUCT(--(B25:K25=B26:K26))&amp;" (of 10)"</f>
@@ -4842,7 +4599,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B32" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B27:K27&lt;B28:K28))&amp;" / "&amp;SUMPRODUCT(--(B27:K27=B28:K28))&amp;" (of 10)"</f>
@@ -4879,55 +4636,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>134</v>
+      <c r="A2" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>2.76189670572929</v>
@@ -4935,7 +4692,7 @@
       <c r="C6" s="7" t="n">
         <v>0.236729011747258</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>2.00515247223236</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -4950,7 +4707,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>1.10400776974611</v>
@@ -4958,7 +4715,7 @@
       <c r="C7" s="7" t="n">
         <v>0.105209847589851</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.996639208844457</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -4973,7 +4730,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.9765625</v>
@@ -4981,7 +4738,7 @@
       <c r="C8" s="7" t="n">
         <v>0.612322598671444</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.8515625</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -4993,12 +4750,12 @@
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>2.67921871733148</v>
@@ -5006,7 +4763,7 @@
       <c r="C9" s="7" t="n">
         <v>0.228425079972053</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>1.95467515661745</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -5021,7 +4778,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>2.79027457863489</v>
@@ -5029,7 +4786,7 @@
       <c r="C10" s="7" t="n">
         <v>0.235780087533817</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>2.05471571023817</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -5040,13 +4797,13 @@
         <v>-0.263615227701564</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -5061,12 +4818,12 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>0.326203400901427</v>
@@ -5074,7 +4831,7 @@
       <c r="C12" s="7" t="n">
         <v>0.0142648931496322</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <v>0.240906842439639</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -5089,7 +4846,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>0.144468598011641</v>
@@ -5097,7 +4854,7 @@
       <c r="C13" s="7" t="n">
         <v>0.0121172907280408</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>0.142736857674104</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -5112,7 +4869,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>0.165625</v>
@@ -5120,7 +4877,7 @@
       <c r="C14" s="7" t="n">
         <v>0.106571205656125</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>0.134375</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -5132,12 +4889,12 @@
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>0.317174222284547</v>
@@ -5145,7 +4902,7 @@
       <c r="C15" s="7" t="n">
         <v>0.0137712373527726</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="12" t="n">
         <v>0.235998892846067</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -5160,7 +4917,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>0.331804254247681</v>
@@ -5168,7 +4925,7 @@
       <c r="C16" s="7" t="n">
         <v>0.0142684938105662</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>0.250335847898947</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -5179,13 +4936,13 @@
         <v>-0.24553153043035</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B17" s="6" t="str">
         <f aca="false">IF(B13&lt;=B12,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -5200,59 +4957,59 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="5" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>2.5</v>
@@ -5272,7 +5029,7 @@
       <c r="G21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
@@ -5289,7 +5046,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>2.5</v>
@@ -5309,7 +5066,7 @@
       <c r="G22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="13" t="n">
         <v>2.5</v>
       </c>
       <c r="I22" s="7" t="n">
@@ -5326,7 +5083,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>0.5</v>
@@ -5346,7 +5103,7 @@
       <c r="G23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
@@ -5363,7 +5120,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>0.5</v>
@@ -5383,7 +5140,7 @@
       <c r="G24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="I24" s="7" t="n">
@@ -5400,7 +5157,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>0</v>
@@ -5420,7 +5177,7 @@
       <c r="G25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="13" t="n">
         <v>2.5</v>
       </c>
       <c r="I25" s="7" t="n">
@@ -5437,7 +5194,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>0</v>
@@ -5457,7 +5214,7 @@
       <c r="G26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="7" t="n">
@@ -5474,7 +5231,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>0</v>
@@ -5494,7 +5251,7 @@
       <c r="G27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="I27" s="7" t="n">
@@ -5511,7 +5268,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>0</v>
@@ -5531,7 +5288,7 @@
       <c r="G28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="7" t="n">
@@ -5548,7 +5305,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B29" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B21:I21&lt;B22:I22))&amp;" / "&amp;SUMPRODUCT(--(B21:I21=B22:I22))&amp;" (of 8)"</f>
@@ -5557,7 +5314,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B30" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B23:I23&lt;B24:I24))&amp;" / "&amp;SUMPRODUCT(--(B23:I23=B24:I24))&amp;" (of 8)"</f>
@@ -5566,7 +5323,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B31" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B25:I25&lt;B26:I26))&amp;" / "&amp;SUMPRODUCT(--(B25:I25=B26:I26))&amp;" (of 8)"</f>
@@ -5575,7 +5332,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B32" s="6" t="str">
         <f aca="false">SUMPRODUCT(--(B27:I27&lt;B28:I28))&amp;" / "&amp;SUMPRODUCT(--(B27:I27=B28:I28))&amp;" (of 8)"</f>
@@ -5584,55 +5341,55 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>139</v>
+      <c r="A36" s="10" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
+      <c r="A38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>2.73942673430051</v>
@@ -5640,7 +5397,7 @@
       <c r="C40" s="7" t="n">
         <v>0.238178760790997</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="12" t="n">
         <v>1.97758376560133</v>
       </c>
       <c r="E40" s="7" t="n">
@@ -5655,7 +5412,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>1.09143289727408</v>
@@ -5663,7 +5420,7 @@
       <c r="C41" s="7" t="n">
         <v>0.0974830673067975</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>1.00614878135162</v>
       </c>
       <c r="E41" s="7" t="n">
@@ -5678,7 +5435,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>1.60416666666667</v>
@@ -5686,7 +5443,7 @@
       <c r="C42" s="7" t="n">
         <v>1.47054411698527</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="12" t="n">
         <v>0.789583333333333</v>
       </c>
       <c r="E42" s="7" t="n">
@@ -5698,12 +5455,12 @@
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>2.65781293270989</v>
@@ -5711,7 +5468,7 @@
       <c r="C43" s="7" t="n">
         <v>0.229373210533129</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>1.92889250624194</v>
       </c>
       <c r="E43" s="7" t="n">
@@ -5726,7 +5483,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>2.76959314951954</v>
@@ -5734,7 +5491,7 @@
       <c r="C44" s="7" t="n">
         <v>0.235862529830526</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="12" t="n">
         <v>2.02964186697718</v>
       </c>
       <c r="E44" s="7" t="n">
@@ -5745,13 +5502,13 @@
         <v>-0.267169668104763</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B45" s="6" t="str">
         <f aca="false">IF(AND(B42&lt;=B41,B41&lt;=B40),"pass",IF(AND(B42-B41&lt;=5,B41-B40&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -5766,12 +5523,12 @@
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>0.323001736427305</v>
@@ -5779,7 +5536,7 @@
       <c r="C46" s="7" t="n">
         <v>0.0151267930497383</v>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="12" t="n">
         <v>0.240540474022652</v>
       </c>
       <c r="E46" s="7" t="n">
@@ -5794,7 +5551,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>0.145120742732053</v>
@@ -5802,7 +5559,7 @@
       <c r="C47" s="7" t="n">
         <v>0.0116606938127742</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="12" t="n">
         <v>0.14425790431115</v>
       </c>
       <c r="E47" s="7" t="n">
@@ -5817,7 +5574,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>0.177083333333333</v>
@@ -5825,7 +5582,7 @@
       <c r="C48" s="7" t="n">
         <v>0.0996216802039931</v>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="12" t="n">
         <v>0.129166666666667</v>
       </c>
       <c r="E48" s="7" t="n">
@@ -5837,12 +5594,12 @@
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>0.314170376581005</v>
@@ -5850,7 +5607,7 @@
       <c r="C49" s="7" t="n">
         <v>0.0144439798355404</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="12" t="n">
         <v>0.235720652615393</v>
       </c>
       <c r="E49" s="7" t="n">
@@ -5865,7 +5622,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>0.328901152222286</v>
@@ -5873,7 +5630,7 @@
       <c r="C50" s="7" t="n">
         <v>0.0146451476898401</v>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="12" t="n">
         <v>0.250188020397275</v>
       </c>
       <c r="E50" s="7" t="n">
@@ -5884,13 +5641,13 @@
         <v>-0.239321544765564</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B51" s="6" t="str">
         <f aca="false">IF(B47&lt;=B46,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -5905,50 +5662,50 @@
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="5" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
+      <c r="A54" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B56" s="7" t="n">
         <v>4.95</v>
@@ -5956,7 +5713,7 @@
       <c r="C56" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="12" t="n">
         <v>2.44</v>
       </c>
       <c r="E56" s="7" t="n">
@@ -5971,7 +5728,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>1.26</v>
@@ -5979,7 +5736,7 @@
       <c r="C57" s="7" t="n">
         <v>0.18</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="12" t="n">
         <v>1.06</v>
       </c>
       <c r="E57" s="7" t="n">
@@ -5994,9 +5751,9 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B58" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" s="12" t="n">
         <v>0.9</v>
       </c>
       <c r="C58" s="7" t="n">
@@ -6014,12 +5771,12 @@
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>4.75</v>
@@ -6027,7 +5784,7 @@
       <c r="C59" s="7" t="n">
         <v>1.17</v>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="12" t="n">
         <v>2.38</v>
       </c>
       <c r="E59" s="7" t="n">
@@ -6042,7 +5799,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>4.89</v>
@@ -6050,7 +5807,7 @@
       <c r="C60" s="7" t="n">
         <v>1.18</v>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="12" t="n">
         <v>2.48</v>
       </c>
       <c r="E60" s="7" t="n">
@@ -6061,13 +5818,13 @@
         <v>-0.492842535787321</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B61" s="6" t="str">
         <f aca="false">IF(AND(B58&lt;=B57,B57&lt;=B56),"pass",IF(AND(B58-B57&lt;=5,B57-B56&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -6082,12 +5839,12 @@
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B62" s="7" t="n">
         <v>0.57</v>
@@ -6095,7 +5852,7 @@
       <c r="C62" s="7" t="n">
         <v>0.09</v>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="12" t="n">
         <v>0.27</v>
       </c>
       <c r="E62" s="7" t="n">
@@ -6110,7 +5867,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B63" s="7" t="n">
         <v>0.18</v>
@@ -6118,7 +5875,7 @@
       <c r="C63" s="7" t="n">
         <v>0.02</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="E63" s="7" t="n">
@@ -6133,9 +5890,9 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" s="12" t="n">
         <v>0.14</v>
       </c>
       <c r="C64" s="7" t="n">
@@ -6153,12 +5910,12 @@
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>0.55</v>
@@ -6166,7 +5923,7 @@
       <c r="C65" s="7" t="n">
         <v>0.09</v>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="12" t="n">
         <v>0.27</v>
       </c>
       <c r="E65" s="7" t="n">
@@ -6181,7 +5938,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>0.566</v>
@@ -6189,7 +5946,7 @@
       <c r="C66" s="7" t="n">
         <v>0.091</v>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="12" t="n">
         <v>0.281</v>
       </c>
       <c r="E66" s="7" t="n">
@@ -6200,13 +5957,13 @@
         <v>-0.503533568904594</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B67" s="6" t="str">
         <f aca="false">IF(B63&lt;=B62,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -6221,12 +5978,12 @@
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -6259,7 +6016,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M140"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -6269,75 +6026,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>145</v>
+      <c r="A2" s="10" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
+      <c r="A4" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>3.73001567125097</v>
@@ -6345,83 +6082,49 @@
       <c r="C6" s="7" t="n">
         <v>0.107439997876835</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>5.91587012221084</v>
+      <c r="D6" s="12" t="n">
+        <v>3.13501807898665</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.0713323549416866</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>3.13501807898665</v>
-      </c>
-      <c r="G6" s="7" t="n">
         <v>0.0560653095759933</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <f aca="false">IF(B6=0,"",D6/B6-1)</f>
-        <v>0.586017497944393</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <f aca="false">IF(B6=0,"",F6/B6-1)</f>
         <v>-0.15951611057569</v>
       </c>
-      <c r="J6" s="8" t="n">
-        <f aca="false">IF(D6=0,"",F6/D6-1)</f>
-        <v>-0.47006644597954</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>1.17274857132071</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0.0876062253185241</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.19151382823872</v>
+        <v>1.46115416579231</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.0947372869618436</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>1.46115416579231</v>
-      </c>
-      <c r="G7" s="7" t="n">
         <v>0.109356823634933</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <f aca="false">IF(B7=0,"",D7/B7-1)</f>
-        <v>0.0160010912627864</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <f aca="false">IF(B7=0,"",F7/B7-1)</f>
         <v>0.245922784750697</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <f aca="false">IF(D7=0,"",F7/D7-1)</f>
-        <v>0.226300636352803</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="M7" s="6"/>
+      <c r="G7" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>1</v>
@@ -6429,43 +6132,26 @@
       <c r="C8" s="7" t="n">
         <v>1.22474487139159</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>4.75</v>
+      <c r="D8" s="12" t="n">
+        <v>0.75</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>6.3688696014285</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G8" s="7" t="n">
         <v>1.14564392373896</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <f aca="false">IF(B8=0,"",D8/B8-1)</f>
-        <v>3.75</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <f aca="false">IF(B8=0,"",F8/B8-1)</f>
         <v>-0.25</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <f aca="false">IF(D8=0,"",F8/D8-1)</f>
-        <v>-0.842105263157895</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>161</v>
+      <c r="G8" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>3.60388839569416</v>
@@ -6473,41 +6159,24 @@
       <c r="C9" s="7" t="n">
         <v>0.104299491238072</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>5.68308025928241</v>
+      <c r="D9" s="12" t="n">
+        <v>3.05216444071164</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.0679779874365291</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>3.05216444071164</v>
-      </c>
-      <c r="G9" s="7" t="n">
         <v>0.0557717470093855</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <f aca="false">IF(B9=0,"",D9/B9-1)</f>
-        <v>0.57693014746861</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <f aca="false">IF(B9=0,"",F9/B9-1)</f>
         <v>-0.153091298732144</v>
       </c>
-      <c r="J9" s="8" t="n">
-        <f aca="false">IF(D9=0,"",F9/D9-1)</f>
-        <v>-0.462938353593297</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M9" s="6"/>
+      <c r="G9" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>3.7211635599533</v>
@@ -6515,41 +6184,24 @@
       <c r="C10" s="7" t="n">
         <v>0.107927974125573</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>5.81875981677413</v>
+      <c r="D10" s="12" t="n">
+        <v>3.18882418536163</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.0701778090176693</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>3.18882418536163</v>
-      </c>
-      <c r="G10" s="7" t="n">
         <v>0.0607226611636084</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <f aca="false">IF(B10=0,"",D10/B10-1)</f>
-        <v>0.563693646631095</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <f aca="false">IF(B10=0,"",F10/B10-1)</f>
         <v>-0.143057236268957</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <f aca="false">IF(D10=0,"",F10/D10-1)</f>
-        <v>-0.451975285838574</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="str">
         <f aca="false">IF(AND(B8&lt;=B7,B7&lt;=B6),"pass",IF(AND(B8-B7&lt;=5,B7-B6&lt;=5),"pass (tol. 5 s)","fail"))</f>
@@ -6558,24 +6210,16 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6" t="str">
         <f aca="false">IF(AND(D8&lt;=D7,D7&lt;=D6),"pass",IF(AND(D8-D7&lt;=5,D7-D6&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass (tol. 5 s)</v>
+        <v>pass</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="6" t="str">
-        <f aca="false">IF(AND(F8&lt;=F7,F7&lt;=F6),"pass",IF(AND(F8-F7&lt;=5,F7-F6&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>0.525440011413682</v>
@@ -6583,83 +6227,49 @@
       <c r="C12" s="7" t="n">
         <v>0.0162100355248492</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.750114777072293</v>
+      <c r="D12" s="12" t="n">
+        <v>0.406849665962055</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.0138254449331872</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>0.406849665962055</v>
-      </c>
-      <c r="G12" s="7" t="n">
         <v>0.00626438635996668</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <f aca="false">IF(B12=0,"",D12/B12-1)</f>
-        <v>0.427593561164347</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <f aca="false">IF(B12=0,"",F12/B12-1)</f>
         <v>-0.225697211623764</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <f aca="false">IF(D12=0,"",F12/D12-1)</f>
-        <v>-0.457616782927548</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B13" s="12" t="n">
         <v>0.180906280359782</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0.0130267352759715</v>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>0.172901177140687</v>
+      <c r="D13" s="7" t="n">
+        <v>0.22202771643367</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.0126886761746455</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>0.22202771643367</v>
-      </c>
-      <c r="G13" s="7" t="n">
         <v>0.0148645460915265</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <f aca="false">IF(B13=0,"",D13/B13-1)</f>
-        <v>-0.0442500017311402</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <f aca="false">IF(B13=0,"",F13/B13-1)</f>
         <v>0.22730795189701</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <f aca="false">IF(D13=0,"",F13/D13-1)</f>
-        <v>0.284130739335622</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="M13" s="6"/>
+      <c r="G13" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>0.2</v>
@@ -6667,43 +6277,26 @@
       <c r="C14" s="7" t="n">
         <v>0.244948974278318</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>0.2</v>
+      <c r="D14" s="12" t="n">
+        <v>0.15</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.244948974278318</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G14" s="7" t="n">
         <v>0.229128784747792</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <f aca="false">IF(B14=0,"",D14/B14-1)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <f aca="false">IF(B14=0,"",F14/B14-1)</f>
         <v>-0.25</v>
       </c>
-      <c r="J14" s="8" t="n">
-        <f aca="false">IF(D14=0,"",F14/D14-1)</f>
-        <v>-0.25</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>161</v>
+      <c r="G14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>0.508456547084597</v>
@@ -6711,41 +6304,24 @@
       <c r="C15" s="7" t="n">
         <v>0.0156380208525405</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>0.721585410470605</v>
+      <c r="D15" s="12" t="n">
+        <v>0.397702236482198</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.0132165695366265</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>0.397702236482198</v>
-      </c>
-      <c r="G15" s="7" t="n">
         <v>0.0063698352216099</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <f aca="false">IF(B15=0,"",D15/B15-1)</f>
-        <v>0.419168293943804</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <f aca="false">IF(B15=0,"",F15/B15-1)</f>
         <v>-0.217824534343092</v>
       </c>
-      <c r="J15" s="8" t="n">
-        <f aca="false">IF(D15=0,"",F15/D15-1)</f>
-        <v>-0.448849393694332</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>0.526277913087023</v>
@@ -6753,41 +6329,24 @@
       <c r="C16" s="7" t="n">
         <v>0.0160129811344642</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>0.740214070553919</v>
+      <c r="D16" s="12" t="n">
+        <v>0.418065335812438</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.0136166891591962</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>0.418065335812438</v>
-      </c>
-      <c r="G16" s="7" t="n">
         <v>0.00721294974255258</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <f aca="false">IF(B16=0,"",D16/B16-1)</f>
-        <v>0.406507953586722</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <f aca="false">IF(B16=0,"",F16/B16-1)</f>
         <v>-0.205618694198727</v>
       </c>
-      <c r="J16" s="8" t="n">
-        <f aca="false">IF(D16=0,"",F16/D16-1)</f>
-        <v>-0.435210228441632</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M16" s="6"/>
+      <c r="G16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B17" s="6" t="str">
         <f aca="false">IF(B13&lt;=B12,"pass (amb n/a)","fail (amb n/a)")</f>
@@ -6799,74 +6358,66 @@
         <v>pass (amb n/a)</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="F17" s="6" t="str">
-        <f aca="false">IF(F13&lt;=F12,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>0</v>
@@ -6886,7 +6437,7 @@
       <c r="G21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" s="13" t="n">
         <v>2.5</v>
       </c>
       <c r="I21" s="7" t="n">
@@ -6909,7 +6460,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>0</v>
@@ -6929,7 +6480,7 @@
       <c r="G22" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="13" t="n">
         <v>5</v>
       </c>
       <c r="I22" s="7" t="n">
@@ -6952,7 +6503,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>0</v>
@@ -6972,7 +6523,7 @@
       <c r="G23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="I23" s="7" t="n">
@@ -6995,7 +6546,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>0</v>
@@ -7015,7 +6566,7 @@
       <c r="G24" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="I24" s="7" t="n">
@@ -7038,13 +6589,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
@@ -7053,35 +6604,35 @@
         <v>0</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="10" t="n">
-        <v>15</v>
+      <c r="H25" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="7" t="n">
         <f aca="false">AVERAGE(B25:K25)</f>
-        <v>4.75</v>
+        <v>0.75</v>
       </c>
       <c r="M25" s="7" t="n">
         <f aca="false">STDEV(B25:K25)</f>
-        <v>6.71337802037428</v>
+        <v>1.20761472884912</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>0</v>
@@ -7099,9 +6650,9 @@
         <v>0</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H26" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="7" t="n">
@@ -7115,22 +6666,22 @@
       </c>
       <c r="L26" s="7" t="n">
         <f aca="false">AVERAGE(B26:K26)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M26" s="7" t="n">
         <f aca="false">STDEV(B26:K26)</f>
-        <v>0</v>
+        <v>0.790569415042095</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -7144,30 +6695,30 @@
       <c r="G27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="7" t="n">
         <f aca="false">AVERAGE(B27:K27)</f>
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M27" s="7" t="n">
         <f aca="false">STDEV(B27:K27)</f>
-        <v>0.258198889747161</v>
+        <v>0.241522945769824</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>0</v>
@@ -7185,9 +6736,9 @@
         <v>0</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="7" t="n">
@@ -7201,2409 +6752,1131 @@
       </c>
       <c r="L28" s="7" t="n">
         <f aca="false">AVERAGE(B28:K28)</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M28" s="7" t="n">
         <f aca="false">STDEV(B28:K28)</f>
-        <v>0</v>
+        <v>0.158113883008419</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <f aca="false">AVERAGE(B29:K29)</f>
-        <v>0.75</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <f aca="false">STDEV(B29:K29)</f>
-        <v>1.20761472884912</v>
+        <v>116</v>
+      </c>
+      <c r="B29" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B21:K21&lt;B22:K22))&amp;" / "&amp;SUMPRODUCT(--(B21:K21=B22:K22))&amp;" (of 10)"</f>
+        <v>8 / 2 (of 10)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <f aca="false">AVERAGE(B30:K30)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M30" s="7" t="n">
-        <f aca="false">STDEV(B30:K30)</f>
-        <v>0.790569415042095</v>
+        <v>117</v>
+      </c>
+      <c r="B30" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B23:K23&lt;B24:K24))&amp;" / "&amp;SUMPRODUCT(--(B23:K23=B24:K24))&amp;" (of 10)"</f>
+        <v>4 / 6 (of 10)</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="7" t="n">
-        <f aca="false">AVERAGE(B31:K31)</f>
-        <v>0.15</v>
-      </c>
-      <c r="M31" s="7" t="n">
-        <f aca="false">STDEV(B31:K31)</f>
-        <v>0.241522945769824</v>
+        <v>147</v>
+      </c>
+      <c r="B31" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B25:K25&lt;B26:K26))&amp;" / "&amp;SUMPRODUCT(--(B25:K25=B26:K26))&amp;" (of 10)"</f>
+        <v>1 / 6 (of 10)</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <f aca="false">AVERAGE(B32:K32)</f>
-        <v>0.05</v>
-      </c>
-      <c r="M32" s="7" t="n">
-        <f aca="false">STDEV(B32:K32)</f>
-        <v>0.158113883008419</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B21:K21&lt;B22:K22))&amp;" / "&amp;SUMPRODUCT(--(B21:K21=B22:K22))&amp;" (of 10)"</f>
-        <v>8 / 2 (of 10)</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B34" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B23:K23&lt;B24:K24))&amp;" / "&amp;SUMPRODUCT(--(B23:K23=B24:K24))&amp;" (of 10)"</f>
-        <v>4 / 6 (of 10)</v>
+        <v>148</v>
+      </c>
+      <c r="B32" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B27:K27&lt;B28:K28))&amp;" / "&amp;SUMPRODUCT(--(B27:K27=B28:K28))&amp;" (of 10)"</f>
+        <v>1 / 6 (of 10)</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B35" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B25:K25&lt;B26:K26))&amp;" / "&amp;SUMPRODUCT(--(B25:K25=B26:K26))&amp;" (of 10)"</f>
-        <v>0 / 6 (of 10)</v>
+      <c r="A35" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B36" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B27:K27&lt;B28:K28))&amp;" / "&amp;SUMPRODUCT(--(B27:K27=B28:K28))&amp;" (of 10)"</f>
-        <v>0 / 6 (of 10)</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B37" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B29:K29&lt;B30:K30))&amp;" / "&amp;SUMPRODUCT(--(B29:K29=B30:K30))&amp;" (of 10)"</f>
-        <v>1 / 6 (of 10)</v>
+      <c r="A36" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B38" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B31:K31&lt;B32:K32))&amp;" / "&amp;SUMPRODUCT(--(B31:K31=B32:K32))&amp;" (of 10)"</f>
-        <v>1 / 6 (of 10)</v>
-      </c>
+      <c r="A38" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>16.6253289847842</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1.16730740243032</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>17.0993937283172</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>2.80382508792183</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <f aca="false">IF(B40=0,"",D40/B40-1)</f>
+        <v>0.0285146082803451</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>177</v>
-      </c>
+      <c r="A41" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>8.31010824058173</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>1.66291852160493</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>5.77119266143125</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>4.62472264379756</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <f aca="false">IF(B41=0,"",D41/B41-1)</f>
+        <v>-0.305521360931485</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>178</v>
-      </c>
+      <c r="A42" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>52.0072110384704</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>463.57307945997</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <f aca="false">IF(B42=0,"",D42/B42-1)</f>
+        <v>6.27272727272727</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>16.2028073110655</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>1.17438918053595</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>16.550201957309</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>2.86091571297782</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <f aca="false">IF(B43=0,"",D43/B43-1)</f>
+        <v>0.021440398541694</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
+      <c r="A44" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>17.0011187356766</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>1.30314780689987</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>17.2651837725786</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>3.3469985993183</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <f aca="false">IF(B44=0,"",D44/B44-1)</f>
+        <v>0.0155322153210906</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="B45" s="6" t="str">
+        <f aca="false">IF(AND(B42&lt;=B41,B41&lt;=B40),"pass",IF(AND(B42-B41&lt;=5,B41-B40&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>fail</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6" t="str">
+        <f aca="false">IF(AND(D42&lt;=D41,D41&lt;=D40),"pass",IF(AND(D42-D41&lt;=5,D41-D40&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>fail</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="13" t="n">
-        <v>3.73001567125097</v>
+        <v>56</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>1.11825075698106</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>0.107439997876835</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>5.91587012221084</v>
+        <v>0.0278516114051082</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>0.454753547989103</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0.0713323549416866</v>
+        <v>0.0418109483048829</v>
       </c>
       <c r="F46" s="8" t="n">
         <f aca="false">IF(B46=0,"",D46/B46-1)</f>
-        <v>0.586017497944393</v>
+        <v>-0.593334907085778</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="13" t="n">
-        <v>1.17274857132071</v>
+        <v>57</v>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.331176296550822</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.0876062253185241</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>1.19151382823872</v>
+        <v>0.025560280405501</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>0.196607771009584</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.0947372869618436</v>
+        <v>0.0305091949599643</v>
       </c>
       <c r="F47" s="8" t="n">
         <f aca="false">IF(B47=0,"",D47/B47-1)</f>
-        <v>0.0160010912627864</v>
+        <v>-0.406335015346088</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="13" t="n">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>0.25</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>1.22474487139159</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>4.75</v>
+        <v>0.25</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>6.3688696014285</v>
+        <v>0.4</v>
       </c>
       <c r="F48" s="8" t="n">
         <f aca="false">IF(B48=0,"",D48/B48-1)</f>
-        <v>3.75</v>
+        <v>-0.2</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" s="13" t="n">
-        <v>3.60388839569416</v>
+        <v>59</v>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>1.07797483506242</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0.104299491238072</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>5.68308025928241</v>
+        <v>0.0268899626968498</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>0.441543329746139</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.0679779874365291</v>
+        <v>0.0411504042255639</v>
       </c>
       <c r="F49" s="8" t="n">
         <f aca="false">IF(B49=0,"",D49/B49-1)</f>
-        <v>0.57693014746861</v>
+        <v>-0.590395512599723</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="13" t="n">
-        <v>3.7211635599533</v>
+        <v>60</v>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>1.11291406653454</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>0.107927974125573</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>5.81875981677413</v>
+        <v>0.0280710610871536</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0.46067059717621</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.0701778090176693</v>
+        <v>0.0432526850564914</v>
       </c>
       <c r="F50" s="8" t="n">
         <f aca="false">IF(B50=0,"",D50/B50-1)</f>
-        <v>0.563693646631095</v>
+        <v>-0.586068133175209</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="B51" s="6" t="str">
-        <f aca="false">IF(AND(B48&lt;=B47,B47&lt;=B46),"pass",IF(AND(B48-B47&lt;=5,B47-B46&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
+        <f aca="false">IF(B47&lt;=B46,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6" t="str">
-        <f aca="false">IF(AND(D48&lt;=D47,D47&lt;=D46),"pass",IF(AND(D48-D47&lt;=5,D47-D46&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass (tol. 5 s)</v>
+        <f aca="false">IF(D47&lt;=D46,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52" s="13" t="n">
-        <v>0.525440011413682</v>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>0.0162100355248492</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0.750114777072293</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0.0138254449331872</v>
-      </c>
-      <c r="F52" s="8" t="n">
-        <f aca="false">IF(B52=0,"",D52/B52-1)</f>
-        <v>0.427593561164347</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="5"/>
+        <v>105</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>0.180906280359782</v>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>0.0130267352759715</v>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>0.172901177140687</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>0.0126886761746455</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <f aca="false">IF(B53=0,"",D53/B53-1)</f>
-        <v>-0.0442500017311402</v>
-      </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="5"/>
+      <c r="A53" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>0.244948974278318</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0.244948974278318</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <f aca="false">IF(B54=0,"",D54/B54-1)</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="5" t="s">
-        <v>63</v>
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B55" s="13" t="n">
-        <v>0.508456547084597</v>
+        <v>47</v>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>15.7620669785379</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0.0156380208525405</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>0.721585410470605</v>
+        <v>1.44743461023039</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>13.7610665997438</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0.0132165695366265</v>
+        <v>1.71595826916205</v>
       </c>
       <c r="F55" s="8" t="n">
         <f aca="false">IF(B55=0,"",D55/B55-1)</f>
-        <v>0.419168293943804</v>
+        <v>-0.126950379129758</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="13" t="n">
-        <v>0.526277913087023</v>
+        <v>48</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>7.71363064685002</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>0.0160129811344642</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0.740214070553919</v>
+        <v>1.38597408835516</v>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>4.59825327510917</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.0136166891591962</v>
+        <v>0.529738151453594</v>
       </c>
       <c r="F56" s="8" t="n">
         <f aca="false">IF(B56=0,"",D56/B56-1)</f>
-        <v>0.406507953586722</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>110</v>
-      </c>
+        <v>-0.403879510748037</v>
+      </c>
+      <c r="G56" s="6"/>
       <c r="H56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B57" s="6" t="str">
-        <f aca="false">IF(B53&lt;=B52,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6" t="str">
-        <f aca="false">IF(D53&lt;=D52,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>2.04124145231932</v>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <f aca="false">IF(B57=0,"",D57/B57-1)</f>
+        <v>-1</v>
+      </c>
       <c r="G57" s="6"/>
       <c r="H57" s="5" t="s">
-        <v>118</v>
-      </c>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>15.3494260371416</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>1.44095371168836</v>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>13.2976366987359</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>1.6431525627768</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <f aca="false">IF(B58=0,"",D58/B58-1)</f>
+        <v>-0.133672056104306</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
+      <c r="A59" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>16.0787040385087</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>1.56071952160253</v>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>13.759763195124</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>1.68208316924463</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <f aca="false">IF(B59=0,"",D59/B59-1)</f>
+        <v>-0.144224362724185</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>90</v>
+      <c r="A60" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="6" t="str">
+        <f aca="false">IF(AND(B57&lt;=B56,B56&lt;=B55),"pass",IF(AND(B57-B56&lt;=5,B56-B55&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>pass</v>
+      </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6" t="str">
+        <f aca="false">IF(AND(D57&lt;=D56,D56&lt;=D55),"pass",IF(AND(D57-D56&lt;=5,D56-D55&lt;=5),"pass (tol. 5 s)","fail"))</f>
+        <v>pass</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0</v>
+        <v>1.10609763383811</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>2.5</v>
+        <v>0.0418164629323776</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>0.503470300589324</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I61" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="7" t="n">
-        <f aca="false">AVERAGE(B61:K61)</f>
-        <v>1</v>
-      </c>
-      <c r="M61" s="7" t="n">
-        <f aca="false">STDEV(B61:K61)</f>
-        <v>1.29099444873581</v>
-      </c>
+        <v>0.0149251034109999</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <f aca="false">IF(B61=0,"",D61/B61-1)</f>
+        <v>-0.544822911479969</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>0</v>
+        <v>0.32076278760949</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>5</v>
+        <v>0.0133859799454869</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>0.228165938864629</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I62" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J62" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K62" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L62" s="7" t="n">
-        <f aca="false">AVERAGE(B62:K62)</f>
-        <v>3</v>
-      </c>
-      <c r="M62" s="7" t="n">
-        <f aca="false">STDEV(B62:K62)</f>
-        <v>1.97202659436654</v>
-      </c>
+        <v>0.020704997977636</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <f aca="false">IF(B62=0,"",D62/B62-1)</f>
+        <v>-0.28867702963597</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>0.5</v>
+        <v>0.235702260395516</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I63" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="7" t="n">
-        <f aca="false">AVERAGE(B63:K63)</f>
-        <v>0.2</v>
-      </c>
-      <c r="M63" s="7" t="n">
-        <f aca="false">STDEV(B63:K63)</f>
-        <v>0.258198889747161</v>
+      <c r="F63" s="8" t="n">
+        <f aca="false">IF(B63=0,"",D63/B63-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>0</v>
+        <v>1.06594748726485</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>0.5</v>
+        <v>0.0401134522193368</v>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>0.489538391955466</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H64" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I64" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J64" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K64" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L64" s="7" t="n">
-        <f aca="false">AVERAGE(B64:K64)</f>
-        <v>0.4</v>
-      </c>
-      <c r="M64" s="7" t="n">
-        <f aca="false">STDEV(B64:K64)</f>
-        <v>0.210818510677892</v>
-      </c>
+        <v>0.0151621883576196</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <f aca="false">IF(B64=0,"",D64/B64-1)</f>
+        <v>-0.540748115827369</v>
+      </c>
+      <c r="G64" s="6"/>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0</v>
+        <v>1.10002594899126</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="D65" s="7" t="n">
-        <v>0</v>
+        <v>0.0416015645457965</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>0.511153789717403</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="I65" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="7" t="n">
-        <f aca="false">AVERAGE(B65:K65)</f>
-        <v>4.75</v>
-      </c>
-      <c r="M65" s="7" t="n">
-        <f aca="false">STDEV(B65:K65)</f>
-        <v>6.71337802037428</v>
-      </c>
+        <v>0.0169298719404022</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <f aca="false">IF(B65=0,"",D65/B65-1)</f>
+        <v>-0.535325698283628</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="7" t="n">
-        <f aca="false">AVERAGE(B66:K66)</f>
-        <v>0</v>
-      </c>
-      <c r="M66" s="7" t="n">
-        <f aca="false">STDEV(B66:K66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I67" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="7" t="n">
-        <f aca="false">AVERAGE(B67:K67)</f>
-        <v>0.2</v>
-      </c>
-      <c r="M67" s="7" t="n">
-        <f aca="false">STDEV(B67:K67)</f>
-        <v>0.258198889747161</v>
+        <v>104</v>
+      </c>
+      <c r="B66" s="6" t="str">
+        <f aca="false">IF(B62&lt;=B61,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6" t="str">
+        <f aca="false">IF(D62&lt;=D61,"pass (amb n/a)","fail (amb n/a)")</f>
+        <v>pass (amb n/a)</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="7" t="n">
-        <f aca="false">AVERAGE(B68:K68)</f>
-        <v>0</v>
-      </c>
-      <c r="M68" s="7" t="n">
-        <f aca="false">STDEV(B68:K68)</f>
-        <v>0</v>
-      </c>
+      <c r="A68" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B69" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B61:K61&lt;B62:K62))&amp;" / "&amp;SUMPRODUCT(--(B61:K61=B62:K62))&amp;" (of 10)"</f>
-        <v>8 / 2 (of 10)</v>
+      <c r="A69" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B70" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B63:K63&lt;B64:K64))&amp;" / "&amp;SUMPRODUCT(--(B63:K63=B64:K64))&amp;" (of 10)"</f>
-        <v>4 / 6 (of 10)</v>
+        <v>108</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7" t="n">
+        <f aca="false">AVERAGE(B70:K70)</f>
+        <v>22</v>
+      </c>
+      <c r="M70" s="7" t="n">
+        <f aca="false">STDEV(B70:K70)</f>
+        <v>54.8204138782058</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B71" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B65:K65&lt;B66:K66))&amp;" / "&amp;SUMPRODUCT(--(B65:K65=B66:K66))&amp;" (of 10)"</f>
-        <v>0 / 6 (of 10)</v>
+        <v>109</v>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <f aca="false">AVERAGE(B71:K71)</f>
+        <v>23.5</v>
+      </c>
+      <c r="M71" s="7" t="n">
+        <f aca="false">STDEV(B71:K71)</f>
+        <v>53.5049322752378</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B72" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B67:K67&lt;B68:K68))&amp;" / "&amp;SUMPRODUCT(--(B67:K67=B68:K68))&amp;" (of 10)"</f>
-        <v>0 / 6 (of 10)</v>
+        <v>110</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <f aca="false">AVERAGE(B72:K72)</f>
+        <v>0.25</v>
+      </c>
+      <c r="M72" s="7" t="n">
+        <f aca="false">STDEV(B72:K72)</f>
+        <v>0.263523138347365</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <f aca="false">AVERAGE(B73:K73)</f>
+        <v>0.4</v>
+      </c>
+      <c r="M73" s="7" t="n">
+        <f aca="false">STDEV(B73:K73)</f>
+        <v>0.316227766016838</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>1550</v>
+      </c>
+      <c r="L74" s="7" t="n">
+        <f aca="false">AVERAGE(B74:K74)</f>
+        <v>160</v>
+      </c>
+      <c r="M74" s="7" t="n">
+        <f aca="false">STDEV(B74:K74)</f>
+        <v>488.648931010575</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>181</v>
+      <c r="A75" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>1550</v>
+      </c>
+      <c r="L75" s="7" t="n">
+        <f aca="false">AVERAGE(B75:K75)</f>
+        <v>158.25</v>
+      </c>
+      <c r="M75" s="7" t="n">
+        <f aca="false">STDEV(B75:K75)</f>
+        <v>489.072321963849</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="11" t="s">
-        <v>182</v>
+      <c r="A76" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <f aca="false">AVERAGE(B76:K76)</f>
+        <v>0.2</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <f aca="false">STDEV(B76:K76)</f>
+        <v>0.421637021355784</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <f aca="false">AVERAGE(B77:K77)</f>
+        <v>0.25</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <f aca="false">STDEV(B77:K77)</f>
+        <v>0.353553390593274</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
+      <c r="A78" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B70:K70&lt;B71:K71))&amp;" / "&amp;SUMPRODUCT(--(B70:K70=B71:K71))&amp;" (of 10)"</f>
+        <v>6 / 2 (of 10)</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>59</v>
+      <c r="A79" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B79" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B72:K72&lt;B73:K73))&amp;" / "&amp;SUMPRODUCT(--(B72:K72=B73:K73))&amp;" (of 10)"</f>
+        <v>4 / 5 (of 10)</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B80" s="13" t="n">
-        <v>3.69527996514097</v>
-      </c>
-      <c r="C80" s="7" t="n">
-        <v>0.096525433049008</v>
-      </c>
-      <c r="D80" s="7" t="n">
-        <v>5.93606896759782</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>0.0758671934643359</v>
-      </c>
-      <c r="F80" s="8" t="n">
-        <f aca="false">IF(B80=0,"",D80/B80-1)</f>
-        <v>0.606392214824072</v>
-      </c>
-      <c r="G80" s="6"/>
-      <c r="H80" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="B80" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B74:K74&lt;B75:K75))&amp;" / "&amp;SUMPRODUCT(--(B74:K74=B75:K75))&amp;" (of 10)"</f>
+        <v>2 / 7 (of 10)</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B81" s="7" t="n">
-        <v>1.16896401182692</v>
-      </c>
-      <c r="C81" s="7" t="n">
-        <v>0.0921351326742655</v>
-      </c>
-      <c r="D81" s="13" t="n">
-        <v>1.14010157584963</v>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>0.0871124339441464</v>
-      </c>
-      <c r="F81" s="8" t="n">
-        <f aca="false">IF(B81=0,"",D81/B81-1)</f>
-        <v>-0.0246906112466064</v>
-      </c>
-      <c r="G81" s="6"/>
-      <c r="H81" s="5"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="8" t="str">
-        <f aca="false">IF(B82=0,"",D82/B82-1)</f>
-        <v/>
-      </c>
-      <c r="G82" s="6"/>
-      <c r="H82" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>3.57058104695067</v>
-      </c>
-      <c r="C83" s="7" t="n">
-        <v>0.093495538063964</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>5.69847219496105</v>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>0.0724277633843349</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <f aca="false">IF(B83=0,"",D83/B83-1)</f>
-        <v>0.595950944686616</v>
-      </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="5"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>3.68644022817255</v>
-      </c>
-      <c r="C84" s="7" t="n">
-        <v>0.0963133118371707</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>5.8267038914822</v>
-      </c>
-      <c r="E84" s="7" t="n">
-        <v>0.0750954363705947</v>
-      </c>
-      <c r="F84" s="8" t="n">
-        <f aca="false">IF(B84=0,"",D84/B84-1)</f>
-        <v>0.580577340425405</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="H84" s="5"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B85" s="6" t="str">
-        <f aca="false">IF(AND(B82&lt;=B81,B81&lt;=B80),"pass",IF(AND(B82-B81&lt;=5,B81-B80&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6" t="str">
-        <f aca="false">IF(AND(D82&lt;=D81,D81&lt;=D80),"pass",IF(AND(D82-D81&lt;=5,D81-D80&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B86" s="13" t="n">
-        <v>0.524142779223798</v>
-      </c>
-      <c r="C86" s="7" t="n">
-        <v>0.0175312047652415</v>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>0.75272377669034</v>
-      </c>
-      <c r="E86" s="7" t="n">
-        <v>0.0113607198492211</v>
-      </c>
-      <c r="F86" s="8" t="n">
-        <f aca="false">IF(B86=0,"",D86/B86-1)</f>
-        <v>0.436104448114399</v>
-      </c>
-      <c r="G86" s="6"/>
-      <c r="H86" s="5"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B87" s="7" t="n">
-        <v>0.179404232132765</v>
-      </c>
-      <c r="C87" s="7" t="n">
-        <v>0.0126959205915095</v>
-      </c>
-      <c r="D87" s="13" t="n">
-        <v>0.171068729827226</v>
-      </c>
-      <c r="E87" s="7" t="n">
-        <v>0.0117730486931533</v>
-      </c>
-      <c r="F87" s="8" t="n">
-        <f aca="false">IF(B87=0,"",D87/B87-1)</f>
-        <v>-0.0464621274896717</v>
-      </c>
-      <c r="G87" s="6"/>
-      <c r="H87" s="5"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="8" t="str">
-        <f aca="false">IF(B88=0,"",D88/B88-1)</f>
-        <v/>
-      </c>
-      <c r="G88" s="6"/>
-      <c r="H88" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B89" s="13" t="n">
-        <v>0.507123502070496</v>
-      </c>
-      <c r="C89" s="7" t="n">
-        <v>0.0167552809913015</v>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>0.723901124702558</v>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>0.0106797975135466</v>
-      </c>
-      <c r="F89" s="8" t="n">
-        <f aca="false">IF(B89=0,"",D89/B89-1)</f>
-        <v>0.427465147537035</v>
-      </c>
-      <c r="G89" s="6"/>
-      <c r="H89" s="5"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B90" s="13" t="n">
-        <v>0.524642957106457</v>
-      </c>
-      <c r="C90" s="7" t="n">
-        <v>0.0168949192105176</v>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>0.742273975685029</v>
-      </c>
-      <c r="E90" s="7" t="n">
-        <v>0.0107957773150188</v>
-      </c>
-      <c r="F90" s="8" t="n">
-        <f aca="false">IF(B90=0,"",D90/B90-1)</f>
-        <v>0.414817383194972</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="H90" s="5"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B91" s="6" t="str">
-        <f aca="false">IF(B87&lt;=B86,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6" t="str">
-        <f aca="false">IF(D87&lt;=D86,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B97" s="12"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="12"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B99" s="13" t="n">
-        <v>16.6253289847842</v>
-      </c>
-      <c r="C99" s="7" t="n">
-        <v>1.16730740243032</v>
-      </c>
-      <c r="D99" s="7" t="n">
-        <v>17.0993937283172</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>2.80382508792183</v>
-      </c>
-      <c r="F99" s="8" t="n">
-        <f aca="false">IF(B99=0,"",D99/B99-1)</f>
-        <v>0.0285146082803451</v>
-      </c>
-      <c r="G99" s="6"/>
-      <c r="H99" s="5"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B100" s="7" t="n">
-        <v>8.31010824058173</v>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>1.66291852160493</v>
-      </c>
-      <c r="D100" s="13" t="n">
-        <v>5.77119266143125</v>
-      </c>
-      <c r="E100" s="7" t="n">
-        <v>4.62472264379756</v>
-      </c>
-      <c r="F100" s="8" t="n">
-        <f aca="false">IF(B100=0,"",D100/B100-1)</f>
-        <v>-0.305521360931485</v>
-      </c>
-      <c r="G100" s="6"/>
-      <c r="H100" s="5"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B101" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="C101" s="7" t="n">
-        <v>52.0072110384704</v>
-      </c>
-      <c r="D101" s="7" t="n">
-        <v>160</v>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>463.57307945997</v>
-      </c>
-      <c r="F101" s="8" t="n">
-        <f aca="false">IF(B101=0,"",D101/B101-1)</f>
-        <v>6.27272727272727</v>
-      </c>
-      <c r="G101" s="6"/>
-      <c r="H101" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B102" s="13" t="n">
-        <v>16.2028073110655</v>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>1.17438918053595</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>16.550201957309</v>
-      </c>
-      <c r="E102" s="7" t="n">
-        <v>2.86091571297782</v>
-      </c>
-      <c r="F102" s="8" t="n">
-        <f aca="false">IF(B102=0,"",D102/B102-1)</f>
-        <v>0.021440398541694</v>
-      </c>
-      <c r="G102" s="6"/>
-      <c r="H102" s="5"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B103" s="13" t="n">
-        <v>17.0011187356766</v>
-      </c>
-      <c r="C103" s="7" t="n">
-        <v>1.30314780689987</v>
-      </c>
-      <c r="D103" s="7" t="n">
-        <v>17.2651837725786</v>
-      </c>
-      <c r="E103" s="7" t="n">
-        <v>3.3469985993183</v>
-      </c>
-      <c r="F103" s="8" t="n">
-        <f aca="false">IF(B103=0,"",D103/B103-1)</f>
-        <v>0.0155322153210906</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H103" s="5"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B104" s="6" t="str">
-        <f aca="false">IF(AND(B101&lt;=B100,B100&lt;=B99),"pass",IF(AND(B101-B100&lt;=5,B100-B99&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>fail</v>
-      </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6" t="str">
-        <f aca="false">IF(AND(D101&lt;=D100,D100&lt;=D99),"pass",IF(AND(D101-D100&lt;=5,D100-D99&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>fail</v>
-      </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B105" s="7" t="n">
-        <v>1.11825075698106</v>
-      </c>
-      <c r="C105" s="7" t="n">
-        <v>0.0278516114051082</v>
-      </c>
-      <c r="D105" s="13" t="n">
-        <v>0.454753547989103</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>0.0418109483048829</v>
-      </c>
-      <c r="F105" s="8" t="n">
-        <f aca="false">IF(B105=0,"",D105/B105-1)</f>
-        <v>-0.593334907085778</v>
-      </c>
-      <c r="G105" s="6"/>
-      <c r="H105" s="5"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B106" s="7" t="n">
-        <v>0.331176296550822</v>
-      </c>
-      <c r="C106" s="7" t="n">
-        <v>0.025560280405501</v>
-      </c>
-      <c r="D106" s="13" t="n">
-        <v>0.196607771009584</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>0.0305091949599643</v>
-      </c>
-      <c r="F106" s="8" t="n">
-        <f aca="false">IF(B106=0,"",D106/B106-1)</f>
-        <v>-0.406335015346088</v>
-      </c>
-      <c r="G106" s="6"/>
-      <c r="H106" s="5"/>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B107" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C107" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D107" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F107" s="8" t="n">
-        <f aca="false">IF(B107=0,"",D107/B107-1)</f>
-        <v>-0.2</v>
-      </c>
-      <c r="G107" s="6"/>
-      <c r="H107" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B108" s="7" t="n">
-        <v>1.07797483506242</v>
-      </c>
-      <c r="C108" s="7" t="n">
-        <v>0.0268899626968498</v>
-      </c>
-      <c r="D108" s="13" t="n">
-        <v>0.441543329746139</v>
-      </c>
-      <c r="E108" s="7" t="n">
-        <v>0.0411504042255639</v>
-      </c>
-      <c r="F108" s="8" t="n">
-        <f aca="false">IF(B108=0,"",D108/B108-1)</f>
-        <v>-0.590395512599723</v>
-      </c>
-      <c r="G108" s="6"/>
-      <c r="H108" s="5"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B109" s="7" t="n">
-        <v>1.11291406653454</v>
-      </c>
-      <c r="C109" s="7" t="n">
-        <v>0.0280710610871536</v>
-      </c>
-      <c r="D109" s="13" t="n">
-        <v>0.46067059717621</v>
-      </c>
-      <c r="E109" s="7" t="n">
-        <v>0.0432526850564914</v>
-      </c>
-      <c r="F109" s="8" t="n">
-        <f aca="false">IF(B109=0,"",D109/B109-1)</f>
-        <v>-0.586068133175209</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H109" s="5"/>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B110" s="6" t="str">
-        <f aca="false">IF(B106&lt;=B105,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6" t="str">
-        <f aca="false">IF(D106&lt;=D105,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B112" s="12"/>
-      <c r="C112" s="12"/>
-      <c r="D112" s="12"/>
-      <c r="E112" s="12"/>
-      <c r="F112" s="12"/>
-      <c r="G112" s="12"/>
-      <c r="H112" s="12"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B114" s="7" t="n">
-        <v>15.7620669785379</v>
-      </c>
-      <c r="C114" s="7" t="n">
-        <v>1.44743461023039</v>
-      </c>
-      <c r="D114" s="13" t="n">
-        <v>13.7610665997438</v>
-      </c>
-      <c r="E114" s="7" t="n">
-        <v>1.71595826916205</v>
-      </c>
-      <c r="F114" s="8" t="n">
-        <f aca="false">IF(B114=0,"",D114/B114-1)</f>
-        <v>-0.126950379129758</v>
-      </c>
-      <c r="G114" s="6"/>
-      <c r="H114" s="5"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B115" s="7" t="n">
-        <v>7.71363064685002</v>
-      </c>
-      <c r="C115" s="7" t="n">
-        <v>1.38597408835516</v>
-      </c>
-      <c r="D115" s="13" t="n">
-        <v>4.59825327510917</v>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>0.529738151453594</v>
-      </c>
-      <c r="F115" s="8" t="n">
-        <f aca="false">IF(B115=0,"",D115/B115-1)</f>
-        <v>-0.403879510748037</v>
-      </c>
-      <c r="G115" s="6"/>
-      <c r="H115" s="5"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B116" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C116" s="7" t="n">
-        <v>2.04124145231932</v>
-      </c>
-      <c r="D116" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="8" t="n">
-        <f aca="false">IF(B116=0,"",D116/B116-1)</f>
-        <v>-1</v>
-      </c>
-      <c r="G116" s="6"/>
-      <c r="H116" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B117" s="7" t="n">
-        <v>15.3494260371416</v>
-      </c>
-      <c r="C117" s="7" t="n">
-        <v>1.44095371168836</v>
-      </c>
-      <c r="D117" s="13" t="n">
-        <v>13.2976366987359</v>
-      </c>
-      <c r="E117" s="7" t="n">
-        <v>1.6431525627768</v>
-      </c>
-      <c r="F117" s="8" t="n">
-        <f aca="false">IF(B117=0,"",D117/B117-1)</f>
-        <v>-0.133672056104306</v>
-      </c>
-      <c r="G117" s="6"/>
-      <c r="H117" s="5"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B118" s="7" t="n">
-        <v>16.0787040385087</v>
-      </c>
-      <c r="C118" s="7" t="n">
-        <v>1.56071952160253</v>
-      </c>
-      <c r="D118" s="13" t="n">
-        <v>13.759763195124</v>
-      </c>
-      <c r="E118" s="7" t="n">
-        <v>1.68208316924463</v>
-      </c>
-      <c r="F118" s="8" t="n">
-        <f aca="false">IF(B118=0,"",D118/B118-1)</f>
-        <v>-0.144224362724185</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="H118" s="5"/>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B119" s="6" t="str">
-        <f aca="false">IF(AND(B116&lt;=B115,B115&lt;=B114),"pass",IF(AND(B116-B115&lt;=5,B115-B114&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6" t="str">
-        <f aca="false">IF(AND(D116&lt;=D115,D115&lt;=D114),"pass",IF(AND(D116-D115&lt;=5,D115-D114&lt;=5),"pass (tol. 5 s)","fail"))</f>
-        <v>pass</v>
-      </c>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B120" s="7" t="n">
-        <v>1.10609763383811</v>
-      </c>
-      <c r="C120" s="7" t="n">
-        <v>0.0418164629323776</v>
-      </c>
-      <c r="D120" s="13" t="n">
-        <v>0.503470300589324</v>
-      </c>
-      <c r="E120" s="7" t="n">
-        <v>0.0149251034109999</v>
-      </c>
-      <c r="F120" s="8" t="n">
-        <f aca="false">IF(B120=0,"",D120/B120-1)</f>
-        <v>-0.544822911479969</v>
-      </c>
-      <c r="G120" s="6"/>
-      <c r="H120" s="5"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B121" s="7" t="n">
-        <v>0.32076278760949</v>
-      </c>
-      <c r="C121" s="7" t="n">
-        <v>0.0133859799454869</v>
-      </c>
-      <c r="D121" s="13" t="n">
-        <v>0.228165938864629</v>
-      </c>
-      <c r="E121" s="7" t="n">
-        <v>0.020704997977636</v>
-      </c>
-      <c r="F121" s="8" t="n">
-        <f aca="false">IF(B121=0,"",D121/B121-1)</f>
-        <v>-0.28867702963597</v>
-      </c>
-      <c r="G121" s="6"/>
-      <c r="H121" s="5"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B122" s="7" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="C122" s="7" t="n">
-        <v>0.235702260395516</v>
-      </c>
-      <c r="D122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="8" t="n">
-        <f aca="false">IF(B122=0,"",D122/B122-1)</f>
-        <v>-1</v>
-      </c>
-      <c r="G122" s="6"/>
-      <c r="H122" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B123" s="7" t="n">
-        <v>1.06594748726485</v>
-      </c>
-      <c r="C123" s="7" t="n">
-        <v>0.0401134522193368</v>
-      </c>
-      <c r="D123" s="13" t="n">
-        <v>0.489538391955466</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>0.0151621883576196</v>
-      </c>
-      <c r="F123" s="8" t="n">
-        <f aca="false">IF(B123=0,"",D123/B123-1)</f>
-        <v>-0.540748115827369</v>
-      </c>
-      <c r="G123" s="6"/>
-      <c r="H123" s="5"/>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B124" s="7" t="n">
-        <v>1.10002594899126</v>
-      </c>
-      <c r="C124" s="7" t="n">
-        <v>0.0416015645457965</v>
-      </c>
-      <c r="D124" s="13" t="n">
-        <v>0.511153789717403</v>
-      </c>
-      <c r="E124" s="7" t="n">
-        <v>0.0169298719404022</v>
-      </c>
-      <c r="F124" s="8" t="n">
-        <f aca="false">IF(B124=0,"",D124/B124-1)</f>
-        <v>-0.535325698283628</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="H124" s="5"/>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B125" s="6" t="str">
-        <f aca="false">IF(B121&lt;=B120,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6" t="str">
-        <f aca="false">IF(D121&lt;=D120,"pass (amb n/a)","fail (amb n/a)")</f>
-        <v>pass (amb n/a)</v>
-      </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
-      <c r="E127" s="12"/>
-      <c r="F127" s="12"/>
-      <c r="G127" s="12"/>
-      <c r="H127" s="12"/>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I128" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J128" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K128" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L128" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M128" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B129" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C129" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="D129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F129" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="K129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="7" t="n">
-        <f aca="false">AVERAGE(B129:K129)</f>
-        <v>22</v>
-      </c>
-      <c r="M129" s="7" t="n">
-        <f aca="false">STDEV(B129:K129)</f>
-        <v>54.8204138782058</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B130" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C130" s="7" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D130" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E130" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G130" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J130" s="7" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="K130" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L130" s="7" t="n">
-        <f aca="false">AVERAGE(B130:K130)</f>
-        <v>23.5</v>
-      </c>
-      <c r="M130" s="7" t="n">
-        <f aca="false">STDEV(B130:K130)</f>
-        <v>53.5049322752378</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B131" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C131" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D131" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F131" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G131" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K131" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="7" t="n">
-        <f aca="false">AVERAGE(B131:K131)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M131" s="7" t="n">
-        <f aca="false">STDEV(B131:K131)</f>
-        <v>0.263523138347365</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B132" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E132" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G132" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J132" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K132" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L132" s="7" t="n">
-        <f aca="false">AVERAGE(B132:K132)</f>
-        <v>0.4</v>
-      </c>
-      <c r="M132" s="7" t="n">
-        <f aca="false">STDEV(B132:K132)</f>
-        <v>0.316227766016838</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="7" t="n">
-        <v>1550</v>
-      </c>
-      <c r="L133" s="7" t="n">
-        <f aca="false">AVERAGE(B133:K133)</f>
-        <v>160</v>
-      </c>
-      <c r="M133" s="7" t="n">
-        <f aca="false">STDEV(B133:K133)</f>
-        <v>488.648931010575</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B134" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F134" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="7" t="n">
-        <v>1550</v>
-      </c>
-      <c r="L134" s="7" t="n">
-        <f aca="false">AVERAGE(B134:K134)</f>
-        <v>158.25</v>
-      </c>
-      <c r="M134" s="7" t="n">
-        <f aca="false">STDEV(B134:K134)</f>
-        <v>489.072321963849</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" s="7" t="n">
-        <f aca="false">AVERAGE(B135:K135)</f>
-        <v>0.2</v>
-      </c>
-      <c r="M135" s="7" t="n">
-        <f aca="false">STDEV(B135:K135)</f>
-        <v>0.421637021355784</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B136" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F136" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="7" t="n">
-        <f aca="false">AVERAGE(B136:K136)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M136" s="7" t="n">
-        <f aca="false">STDEV(B136:K136)</f>
-        <v>0.353553390593274</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B137" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B129:K129&lt;B130:K130))&amp;" / "&amp;SUMPRODUCT(--(B129:K129=B130:K130))&amp;" (of 10)"</f>
-        <v>6 / 2 (of 10)</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B138" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B131:K131&lt;B132:K132))&amp;" / "&amp;SUMPRODUCT(--(B131:K131=B132:K132))&amp;" (of 10)"</f>
-        <v>4 / 5 (of 10)</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B139" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B133:K133&lt;B134:K134))&amp;" / "&amp;SUMPRODUCT(--(B133:K133=B134:K134))&amp;" (of 10)"</f>
+        <v>119</v>
+      </c>
+      <c r="B81" s="6" t="str">
+        <f aca="false">SUMPRODUCT(--(B76:K76&lt;B77:K77))&amp;" / "&amp;SUMPRODUCT(--(B76:K76=B77:K77))&amp;" (of 10)"</f>
         <v>2 / 7 (of 10)</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B140" s="6" t="str">
-        <f aca="false">SUMPRODUCT(--(B135:K135&lt;B136:K136))&amp;" / "&amp;SUMPRODUCT(--(B135:K135=B136:K136))&amp;" (of 10)"</f>
-        <v>2 / 7 (of 10)</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A4:M4"/>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A112:H112"/>
-    <mergeCell ref="A127:H127"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A68:H68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
